--- a/Chấm công/ĐIÊM DANH T3.xlsx
+++ b/Chấm công/ĐIÊM DANH T3.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Duc Anh\Chấm công\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{907BC627-434C-4AB0-96BA-B6C04E161FC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6192D05-B39D-45D8-AE27-EDE3AB77076D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{5F25DB95-9F61-4E14-A6AC-3108B48F6C7D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="10" xr2:uid="{5F25DB95-9F61-4E14-A6AC-3108B48F6C7D}"/>
   </bookViews>
   <sheets>
     <sheet name="DANH SÁCH XE" sheetId="6" r:id="rId1"/>
@@ -19,6 +19,11 @@
     <sheet name="16-02" sheetId="3" r:id="rId4"/>
     <sheet name="17-03" sheetId="4" r:id="rId5"/>
     <sheet name="18-03" sheetId="5" r:id="rId6"/>
+    <sheet name="22-03" sheetId="7" r:id="rId7"/>
+    <sheet name="24-03" sheetId="8" r:id="rId8"/>
+    <sheet name="25-03" sheetId="9" r:id="rId9"/>
+    <sheet name="26-03." sheetId="10" r:id="rId10"/>
+    <sheet name="27-03" sheetId="11" r:id="rId11"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="626" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="905" uniqueCount="104">
   <si>
     <t>HỌ TÊN</t>
   </si>
@@ -315,13 +320,49 @@
   </si>
   <si>
     <t>NAM ĐẢO</t>
+  </si>
+  <si>
+    <t>68HC 002.42</t>
+  </si>
+  <si>
+    <t>68HC 002.40</t>
+  </si>
+  <si>
+    <t>68HC 002.60</t>
+  </si>
+  <si>
+    <t>68HC 002.27</t>
+  </si>
+  <si>
+    <t>68HC 002.62</t>
+  </si>
+  <si>
+    <t>PHƯƠNG CHIM MỒI</t>
+  </si>
+  <si>
+    <t>MAI SĨ BEN</t>
+  </si>
+  <si>
+    <t>TRƯƠNG HOÀNG GIANG</t>
+  </si>
+  <si>
+    <t>DƯƠNG BÍ</t>
+  </si>
+  <si>
+    <t>LÊ NGUYỄN THANH PHONG</t>
+  </si>
+  <si>
+    <t>TRẦN QUỐC VÂN</t>
+  </si>
+  <si>
+    <t>lấy xe của lập chạy</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="13"/>
       <color theme="1"/>
@@ -385,8 +426,41 @@
       <family val="2"/>
       <scheme val="major"/>
     </font>
+    <font>
+      <b/>
+      <sz val="26"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="13"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -429,8 +503,26 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDEEAF6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF595959"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEF2CB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="4">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -471,12 +563,116 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -546,19 +742,79 @@
     <xf numFmtId="0" fontId="8" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1415,10 +1671,10 @@
       </c>
     </row>
     <row r="34" spans="1:7" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A34" s="25" t="s">
+      <c r="A34" s="42" t="s">
         <v>90</v>
       </c>
-      <c r="B34" s="28">
+      <c r="B34" s="26">
         <v>1</v>
       </c>
       <c r="C34" s="6"/>
@@ -1432,8 +1688,8 @@
       <c r="G34" s="11"/>
     </row>
     <row r="35" spans="1:7" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A35" s="25"/>
-      <c r="B35" s="28">
+      <c r="A35" s="42"/>
+      <c r="B35" s="26">
         <f>B34+1</f>
         <v>2</v>
       </c>
@@ -1450,8 +1706,8 @@
       <c r="G35" s="11"/>
     </row>
     <row r="36" spans="1:7" ht="23.25" x14ac:dyDescent="0.35">
-      <c r="A36" s="25"/>
-      <c r="B36" s="28">
+      <c r="A36" s="42"/>
+      <c r="B36" s="26">
         <f t="shared" ref="B36:B68" si="1">B35+1</f>
         <v>3</v>
       </c>
@@ -1466,8 +1722,8 @@
       <c r="G36" s="11"/>
     </row>
     <row r="37" spans="1:7" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A37" s="25"/>
-      <c r="B37" s="28">
+      <c r="A37" s="42"/>
+      <c r="B37" s="26">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
@@ -1484,8 +1740,8 @@
       <c r="G37" s="11"/>
     </row>
     <row r="38" spans="1:7" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A38" s="25"/>
-      <c r="B38" s="28">
+      <c r="A38" s="42"/>
+      <c r="B38" s="26">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
@@ -1498,8 +1754,8 @@
       <c r="G38" s="11"/>
     </row>
     <row r="39" spans="1:7" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A39" s="25"/>
-      <c r="B39" s="28">
+      <c r="A39" s="42"/>
+      <c r="B39" s="26">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
@@ -1514,8 +1770,8 @@
       <c r="G39" s="11"/>
     </row>
     <row r="40" spans="1:7" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A40" s="25"/>
-      <c r="B40" s="28">
+      <c r="A40" s="42"/>
+      <c r="B40" s="26">
         <f t="shared" si="1"/>
         <v>7</v>
       </c>
@@ -1530,8 +1786,8 @@
       <c r="G40" s="11"/>
     </row>
     <row r="41" spans="1:7" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A41" s="25"/>
-      <c r="B41" s="28">
+      <c r="A41" s="42"/>
+      <c r="B41" s="26">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
@@ -1546,8 +1802,8 @@
       <c r="G41" s="11"/>
     </row>
     <row r="42" spans="1:7" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A42" s="25"/>
-      <c r="B42" s="28">
+      <c r="A42" s="42"/>
+      <c r="B42" s="26">
         <f t="shared" si="1"/>
         <v>9</v>
       </c>
@@ -1564,8 +1820,8 @@
       <c r="G42" s="11"/>
     </row>
     <row r="43" spans="1:7" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A43" s="25"/>
-      <c r="B43" s="28">
+      <c r="A43" s="42"/>
+      <c r="B43" s="26">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
@@ -1580,8 +1836,8 @@
       <c r="G43" s="11"/>
     </row>
     <row r="44" spans="1:7" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A44" s="25"/>
-      <c r="B44" s="28">
+      <c r="A44" s="42"/>
+      <c r="B44" s="26">
         <f t="shared" si="1"/>
         <v>11</v>
       </c>
@@ -1598,8 +1854,8 @@
       <c r="G44" s="11"/>
     </row>
     <row r="45" spans="1:7" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A45" s="25"/>
-      <c r="B45" s="28">
+      <c r="A45" s="42"/>
+      <c r="B45" s="26">
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
@@ -1616,8 +1872,8 @@
       <c r="G45" s="11"/>
     </row>
     <row r="46" spans="1:7" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A46" s="25"/>
-      <c r="B46" s="28">
+      <c r="A46" s="42"/>
+      <c r="B46" s="26">
         <f t="shared" si="1"/>
         <v>13</v>
       </c>
@@ -1632,8 +1888,8 @@
       <c r="G46" s="11"/>
     </row>
     <row r="47" spans="1:7" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A47" s="25"/>
-      <c r="B47" s="28">
+      <c r="A47" s="42"/>
+      <c r="B47" s="26">
         <f t="shared" si="1"/>
         <v>14</v>
       </c>
@@ -1648,12 +1904,11 @@
       <c r="G47" s="11"/>
     </row>
     <row r="48" spans="1:7" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A48" s="27" t="s">
+      <c r="A48" s="43" t="s">
         <v>91</v>
       </c>
-      <c r="B48" s="29">
-        <f t="shared" si="1"/>
-        <v>15</v>
+      <c r="B48" s="27">
+        <v>1</v>
       </c>
       <c r="C48" s="6"/>
       <c r="D48" s="6" t="s">
@@ -1664,14 +1919,14 @@
       <c r="G48" s="11"/>
     </row>
     <row r="49" spans="1:7" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A49" s="27"/>
-      <c r="B49" s="29">
-        <f t="shared" si="1"/>
-        <v>16</v>
+      <c r="A49" s="43"/>
+      <c r="B49" s="27">
+        <f>B48+1</f>
+        <v>2</v>
       </c>
       <c r="C49" s="6"/>
       <c r="D49" s="6" t="s">
-        <v>5</v>
+        <v>92</v>
       </c>
       <c r="E49" s="11"/>
       <c r="F49" s="11" t="s">
@@ -1680,28 +1935,28 @@
       <c r="G49" s="11"/>
     </row>
     <row r="50" spans="1:7" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A50" s="27"/>
-      <c r="B50" s="29">
+      <c r="A50" s="43"/>
+      <c r="B50" s="27">
         <f t="shared" si="1"/>
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="C50" s="6"/>
       <c r="D50" s="6" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E50" s="11"/>
       <c r="F50" s="11"/>
       <c r="G50" s="11"/>
     </row>
     <row r="51" spans="1:7" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A51" s="27"/>
-      <c r="B51" s="29">
+      <c r="A51" s="43"/>
+      <c r="B51" s="27">
         <f t="shared" si="1"/>
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="C51" s="6"/>
       <c r="D51" s="6" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E51" s="11"/>
       <c r="F51" s="11" t="s">
@@ -1710,14 +1965,14 @@
       <c r="G51" s="11"/>
     </row>
     <row r="52" spans="1:7" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A52" s="27"/>
-      <c r="B52" s="29">
+      <c r="A52" s="43"/>
+      <c r="B52" s="27">
         <f t="shared" si="1"/>
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="6" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="E52" s="11"/>
       <c r="F52" s="11" t="s">
@@ -1726,14 +1981,14 @@
       <c r="G52" s="11"/>
     </row>
     <row r="53" spans="1:7" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A53" s="27"/>
-      <c r="B53" s="29">
+      <c r="A53" s="43"/>
+      <c r="B53" s="27">
         <f t="shared" si="1"/>
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="C53" s="6"/>
       <c r="D53" s="6" t="s">
-        <v>5</v>
+        <v>93</v>
       </c>
       <c r="E53" s="11"/>
       <c r="F53" s="11" t="s">
@@ -1742,14 +1997,14 @@
       <c r="G53" s="11"/>
     </row>
     <row r="54" spans="1:7" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A54" s="27"/>
-      <c r="B54" s="29">
+      <c r="A54" s="43"/>
+      <c r="B54" s="27">
         <f t="shared" si="1"/>
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="6" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E54" s="11"/>
       <c r="F54" s="13">
@@ -1758,14 +2013,14 @@
       <c r="G54" s="13"/>
     </row>
     <row r="55" spans="1:7" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A55" s="27"/>
-      <c r="B55" s="29">
+      <c r="A55" s="43"/>
+      <c r="B55" s="27">
         <f t="shared" si="1"/>
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="C55" s="6"/>
       <c r="D55" s="6" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E55" s="11"/>
       <c r="F55" s="11" t="s">
@@ -1774,14 +2029,14 @@
       <c r="G55" s="11"/>
     </row>
     <row r="56" spans="1:7" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A56" s="27"/>
-      <c r="B56" s="29">
+      <c r="A56" s="43"/>
+      <c r="B56" s="27">
         <f t="shared" si="1"/>
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="C56" s="6"/>
       <c r="D56" s="6" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E56" s="11"/>
       <c r="F56" s="11" t="s">
@@ -1790,98 +2045,108 @@
       <c r="G56" s="11"/>
     </row>
     <row r="57" spans="1:7" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A57" s="27"/>
-      <c r="B57" s="29">
+      <c r="A57" s="43"/>
+      <c r="B57" s="27">
         <f t="shared" si="1"/>
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="C57" s="6"/>
       <c r="D57" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E57" s="11"/>
       <c r="F57" s="11"/>
       <c r="G57" s="11"/>
     </row>
     <row r="58" spans="1:7" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A58" s="27"/>
-      <c r="B58" s="29">
+      <c r="A58" s="43"/>
+      <c r="B58" s="27">
         <f t="shared" si="1"/>
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="6" t="s">
-        <v>5</v>
+        <v>94</v>
       </c>
       <c r="E58" s="11"/>
       <c r="F58" s="11"/>
       <c r="G58" s="11"/>
     </row>
     <row r="59" spans="1:7" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A59" s="27"/>
-      <c r="B59" s="29">
+      <c r="A59" s="43"/>
+      <c r="B59" s="27">
         <f t="shared" si="1"/>
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="C59" s="6"/>
-      <c r="D59" s="9"/>
+      <c r="D59" s="6" t="s">
+        <v>17</v>
+      </c>
       <c r="E59" s="11"/>
       <c r="F59" s="11"/>
       <c r="G59" s="11"/>
     </row>
     <row r="60" spans="1:7" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A60" s="27"/>
-      <c r="B60" s="29">
+      <c r="A60" s="43"/>
+      <c r="B60" s="27">
         <f t="shared" si="1"/>
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="C60" s="6"/>
-      <c r="D60" s="9"/>
+      <c r="D60" s="6" t="s">
+        <v>95</v>
+      </c>
       <c r="E60" s="11"/>
       <c r="F60" s="11"/>
       <c r="G60" s="11"/>
     </row>
     <row r="61" spans="1:7" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A61" s="27"/>
-      <c r="B61" s="29">
+      <c r="A61" s="43"/>
+      <c r="B61" s="27">
         <f t="shared" si="1"/>
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="C61" s="6"/>
-      <c r="D61" s="9"/>
+      <c r="D61" s="6" t="s">
+        <v>20</v>
+      </c>
       <c r="E61" s="11"/>
       <c r="F61" s="11"/>
       <c r="G61" s="11"/>
     </row>
     <row r="62" spans="1:7" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A62" s="27"/>
-      <c r="B62" s="29">
+      <c r="A62" s="43"/>
+      <c r="B62" s="27">
         <f t="shared" si="1"/>
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="C62" s="6"/>
-      <c r="D62" s="9"/>
+      <c r="D62" s="6" t="s">
+        <v>7</v>
+      </c>
       <c r="E62" s="11"/>
       <c r="F62" s="11"/>
       <c r="G62" s="11"/>
     </row>
     <row r="63" spans="1:7" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A63" s="27"/>
-      <c r="B63" s="29">
+      <c r="A63" s="43"/>
+      <c r="B63" s="27">
         <f t="shared" si="1"/>
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="C63" s="6"/>
-      <c r="D63" s="9"/>
+      <c r="D63" s="6" t="s">
+        <v>96</v>
+      </c>
       <c r="E63" s="11"/>
       <c r="F63" s="11"/>
       <c r="G63" s="11"/>
     </row>
     <row r="64" spans="1:7" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A64" s="27"/>
-      <c r="B64" s="29">
+      <c r="A64" s="43"/>
+      <c r="B64" s="27">
         <f t="shared" si="1"/>
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="9"/>
@@ -1890,10 +2155,10 @@
       <c r="G64" s="11"/>
     </row>
     <row r="65" spans="1:7" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A65" s="27"/>
-      <c r="B65" s="29">
+      <c r="A65" s="43"/>
+      <c r="B65" s="27">
         <f t="shared" si="1"/>
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="C65" s="6"/>
       <c r="D65" s="9"/>
@@ -1902,10 +2167,10 @@
       <c r="G65" s="11"/>
     </row>
     <row r="66" spans="1:7" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A66" s="27"/>
-      <c r="B66" s="29">
+      <c r="A66" s="43"/>
+      <c r="B66" s="27">
         <f t="shared" si="1"/>
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="9"/>
@@ -1914,10 +2179,10 @@
       <c r="G66" s="11"/>
     </row>
     <row r="67" spans="1:7" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A67" s="27"/>
-      <c r="B67" s="29">
+      <c r="A67" s="43"/>
+      <c r="B67" s="27">
         <f t="shared" si="1"/>
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="C67" s="6"/>
       <c r="D67" s="9"/>
@@ -1926,10 +2191,10 @@
       <c r="G67" s="11"/>
     </row>
     <row r="68" spans="1:7" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A68" s="27"/>
-      <c r="B68" s="29">
+      <c r="A68" s="43"/>
+      <c r="B68" s="27">
         <f t="shared" si="1"/>
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="9"/>
@@ -1938,7 +2203,7 @@
       <c r="G68" s="11"/>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A69" s="26"/>
+      <c r="A69" s="25"/>
     </row>
   </sheetData>
   <dataConsolidate/>
@@ -1950,6 +2215,1150 @@
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Enter invoicing Company Name in this cell and slogan in cell below" sqref="B1" xr:uid="{41E3A29E-2315-4A52-A2C2-B2718B4C195F}"/>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B47FF9F-4314-4A27-B71B-F9E2BFDB5A8F}">
+  <dimension ref="A1:E47"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="20" customWidth="1"/>
+    <col min="2" max="2" width="8.21875" customWidth="1"/>
+    <col min="3" max="3" width="27.44140625" customWidth="1"/>
+    <col min="4" max="5" width="18.77734375" customWidth="1"/>
+    <col min="6" max="6" width="20.77734375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="54.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B1" s="15" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="63" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="1"/>
+      <c r="C2" s="16" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="42.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="1:5" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="44" t="s">
+        <v>90</v>
+      </c>
+      <c r="B4" s="28">
+        <v>1</v>
+      </c>
+      <c r="C4" s="29" t="s">
+        <v>86</v>
+      </c>
+      <c r="D4" s="30">
+        <v>1</v>
+      </c>
+      <c r="E4" s="31" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="45"/>
+      <c r="B5" s="32">
+        <v>2</v>
+      </c>
+      <c r="C5" s="33" t="s">
+        <v>87</v>
+      </c>
+      <c r="D5" s="34"/>
+      <c r="E5" s="35" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="45"/>
+      <c r="B6" s="32">
+        <v>3</v>
+      </c>
+      <c r="C6" s="33" t="s">
+        <v>39</v>
+      </c>
+      <c r="D6" s="34">
+        <v>1</v>
+      </c>
+      <c r="E6" s="35" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="45"/>
+      <c r="B7" s="32">
+        <v>4</v>
+      </c>
+      <c r="C7" s="33" t="s">
+        <v>27</v>
+      </c>
+      <c r="D7" s="34">
+        <v>1</v>
+      </c>
+      <c r="E7" s="36" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="45"/>
+      <c r="B8" s="32">
+        <v>5</v>
+      </c>
+      <c r="C8" s="33"/>
+      <c r="D8" s="34"/>
+      <c r="E8" s="36" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="45"/>
+      <c r="B9" s="32">
+        <v>6</v>
+      </c>
+      <c r="C9" s="34"/>
+      <c r="D9" s="34"/>
+      <c r="E9" s="35" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="45"/>
+      <c r="B10" s="32">
+        <v>7</v>
+      </c>
+      <c r="C10" s="34"/>
+      <c r="D10" s="34"/>
+      <c r="E10" s="35" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="45"/>
+      <c r="B11" s="32">
+        <v>8</v>
+      </c>
+      <c r="C11" s="34"/>
+      <c r="D11" s="34"/>
+      <c r="E11" s="35" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="45"/>
+      <c r="B12" s="32">
+        <v>9</v>
+      </c>
+      <c r="C12" s="34"/>
+      <c r="D12" s="34"/>
+      <c r="E12" s="35" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="45"/>
+      <c r="B13" s="32">
+        <v>10</v>
+      </c>
+      <c r="C13" s="34"/>
+      <c r="D13" s="34"/>
+      <c r="E13" s="35" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A14" s="45"/>
+      <c r="B14" s="32">
+        <v>11</v>
+      </c>
+      <c r="C14" s="34"/>
+      <c r="D14" s="34"/>
+      <c r="E14" s="35" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="45"/>
+      <c r="B15" s="32">
+        <v>12</v>
+      </c>
+      <c r="C15" s="34"/>
+      <c r="D15" s="34"/>
+      <c r="E15" s="35" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="45"/>
+      <c r="B16" s="32">
+        <v>13</v>
+      </c>
+      <c r="C16" s="34"/>
+      <c r="D16" s="34"/>
+      <c r="E16" s="35" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="45"/>
+      <c r="B17" s="32">
+        <v>14</v>
+      </c>
+      <c r="C17" s="34"/>
+      <c r="D17" s="34"/>
+      <c r="E17" s="35" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="45"/>
+      <c r="B18" s="32">
+        <v>15</v>
+      </c>
+      <c r="C18" s="34"/>
+      <c r="D18" s="34"/>
+      <c r="E18" s="34"/>
+    </row>
+    <row r="19" spans="1:5" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="46"/>
+      <c r="B19" s="38"/>
+      <c r="C19" s="38"/>
+      <c r="D19" s="38"/>
+      <c r="E19" s="38"/>
+    </row>
+    <row r="20" spans="1:5" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="47" t="s">
+        <v>91</v>
+      </c>
+      <c r="B20" s="32">
+        <v>1</v>
+      </c>
+      <c r="C20" s="39"/>
+      <c r="D20" s="41"/>
+      <c r="E20" s="36" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="48"/>
+      <c r="B21" s="32">
+        <v>2</v>
+      </c>
+      <c r="C21" s="37"/>
+      <c r="D21" s="41"/>
+      <c r="E21" s="36" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A22" s="48"/>
+      <c r="B22" s="32">
+        <v>3</v>
+      </c>
+      <c r="C22" s="39" t="s">
+        <v>28</v>
+      </c>
+      <c r="D22" s="41">
+        <v>0</v>
+      </c>
+      <c r="E22" s="36" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A23" s="48"/>
+      <c r="B23" s="32">
+        <v>4</v>
+      </c>
+      <c r="C23" s="39" t="s">
+        <v>38</v>
+      </c>
+      <c r="D23" s="41">
+        <v>1</v>
+      </c>
+      <c r="E23" s="36" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A24" s="48"/>
+      <c r="B24" s="32">
+        <v>5</v>
+      </c>
+      <c r="C24" s="39" t="s">
+        <v>97</v>
+      </c>
+      <c r="D24" s="41">
+        <v>1</v>
+      </c>
+      <c r="E24" s="36" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A25" s="48"/>
+      <c r="B25" s="32">
+        <v>6</v>
+      </c>
+      <c r="C25" s="39" t="s">
+        <v>34</v>
+      </c>
+      <c r="D25" s="41">
+        <v>1</v>
+      </c>
+      <c r="E25" s="36" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A26" s="48"/>
+      <c r="B26" s="32">
+        <v>7</v>
+      </c>
+      <c r="C26" s="39" t="s">
+        <v>30</v>
+      </c>
+      <c r="D26" s="41">
+        <v>1</v>
+      </c>
+      <c r="E26" s="36" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A27" s="48"/>
+      <c r="B27" s="32">
+        <v>8</v>
+      </c>
+      <c r="C27" s="39" t="s">
+        <v>26</v>
+      </c>
+      <c r="D27" s="41">
+        <v>0</v>
+      </c>
+      <c r="E27" s="36" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A28" s="48"/>
+      <c r="B28" s="32">
+        <v>9</v>
+      </c>
+      <c r="C28" s="39" t="s">
+        <v>98</v>
+      </c>
+      <c r="D28" s="41">
+        <v>0</v>
+      </c>
+      <c r="E28" s="36" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A29" s="48"/>
+      <c r="B29" s="32">
+        <v>10</v>
+      </c>
+      <c r="C29" s="39" t="s">
+        <v>63</v>
+      </c>
+      <c r="D29" s="41">
+        <v>0</v>
+      </c>
+      <c r="E29" s="36" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A30" s="48"/>
+      <c r="B30" s="32">
+        <v>11</v>
+      </c>
+      <c r="C30" s="39" t="s">
+        <v>99</v>
+      </c>
+      <c r="D30" s="41">
+        <v>1</v>
+      </c>
+      <c r="E30" s="36" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A31" s="48"/>
+      <c r="B31" s="32">
+        <v>12</v>
+      </c>
+      <c r="C31" s="39" t="s">
+        <v>31</v>
+      </c>
+      <c r="D31" s="41">
+        <v>1</v>
+      </c>
+      <c r="E31" s="36" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A32" s="48"/>
+      <c r="B32" s="32">
+        <v>13</v>
+      </c>
+      <c r="C32" s="39" t="s">
+        <v>100</v>
+      </c>
+      <c r="D32" s="41">
+        <v>1</v>
+      </c>
+      <c r="E32" s="36" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" ht="42.75" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A33" s="48"/>
+      <c r="B33" s="32">
+        <v>14</v>
+      </c>
+      <c r="C33" s="39" t="s">
+        <v>101</v>
+      </c>
+      <c r="D33" s="41">
+        <v>0</v>
+      </c>
+      <c r="E33" s="36" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A34" s="48"/>
+      <c r="B34" s="32">
+        <v>15</v>
+      </c>
+      <c r="C34" s="39" t="s">
+        <v>36</v>
+      </c>
+      <c r="D34" s="41">
+        <v>1</v>
+      </c>
+      <c r="E34" s="36" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A35" s="48"/>
+      <c r="B35" s="32">
+        <v>16</v>
+      </c>
+      <c r="C35" s="39" t="s">
+        <v>102</v>
+      </c>
+      <c r="D35" s="41">
+        <v>1</v>
+      </c>
+      <c r="E35" s="36" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="48"/>
+      <c r="B36" s="32">
+        <v>17</v>
+      </c>
+      <c r="C36" s="37"/>
+      <c r="D36" s="41"/>
+      <c r="E36" s="40" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="48"/>
+      <c r="B37" s="32">
+        <v>18</v>
+      </c>
+      <c r="C37" s="37"/>
+      <c r="D37" s="41"/>
+      <c r="E37" s="40" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="48"/>
+      <c r="B38" s="32">
+        <v>19</v>
+      </c>
+      <c r="C38" s="37"/>
+      <c r="D38" s="41"/>
+      <c r="E38" s="37"/>
+    </row>
+    <row r="39" spans="1:5" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="48"/>
+      <c r="B39" s="32">
+        <v>20</v>
+      </c>
+      <c r="C39" s="37"/>
+      <c r="D39" s="41"/>
+      <c r="E39" s="37"/>
+    </row>
+    <row r="40" spans="1:5" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="48"/>
+      <c r="B40" s="32">
+        <v>21</v>
+      </c>
+      <c r="C40" s="37"/>
+      <c r="D40" s="41"/>
+      <c r="E40" s="37"/>
+    </row>
+    <row r="41" spans="1:5" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="48"/>
+      <c r="B41" s="32">
+        <v>22</v>
+      </c>
+      <c r="C41" s="37"/>
+      <c r="D41" s="41"/>
+      <c r="E41" s="37"/>
+    </row>
+    <row r="42" spans="1:5" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="48"/>
+      <c r="B42" s="32">
+        <v>23</v>
+      </c>
+      <c r="C42" s="37"/>
+      <c r="D42" s="41"/>
+      <c r="E42" s="37"/>
+    </row>
+    <row r="43" spans="1:5" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="48"/>
+      <c r="B43" s="32">
+        <v>24</v>
+      </c>
+      <c r="C43" s="37"/>
+      <c r="D43" s="41"/>
+      <c r="E43" s="37"/>
+    </row>
+    <row r="44" spans="1:5" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="48"/>
+      <c r="B44" s="32">
+        <v>25</v>
+      </c>
+      <c r="C44" s="37"/>
+      <c r="D44" s="37"/>
+      <c r="E44" s="37"/>
+    </row>
+    <row r="45" spans="1:5" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="48"/>
+      <c r="B45" s="32">
+        <v>26</v>
+      </c>
+      <c r="C45" s="37"/>
+      <c r="D45" s="37"/>
+      <c r="E45" s="37"/>
+    </row>
+    <row r="46" spans="1:5" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="48"/>
+      <c r="B46" s="32">
+        <v>27</v>
+      </c>
+      <c r="C46" s="37"/>
+      <c r="D46" s="37"/>
+      <c r="E46" s="37"/>
+    </row>
+    <row r="47" spans="1:5" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="49"/>
+      <c r="B47" s="32">
+        <v>28</v>
+      </c>
+      <c r="C47" s="34"/>
+      <c r="D47" s="34"/>
+      <c r="E47" s="34"/>
+    </row>
+  </sheetData>
+  <dataConsolidate/>
+  <mergeCells count="2">
+    <mergeCell ref="A4:A19"/>
+    <mergeCell ref="A20:A47"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Enter invoicing Company Name in this cell and slogan in cell below" sqref="B1" xr:uid="{08FD185F-400A-4297-8671-587590F2B017}"/>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{069BE8DC-7F3A-45EA-BFF4-1C7F4AA8AEBC}">
+  <dimension ref="A1:F47"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="20" customWidth="1"/>
+    <col min="2" max="2" width="8.21875" customWidth="1"/>
+    <col min="3" max="3" width="27.44140625" customWidth="1"/>
+    <col min="4" max="5" width="18.77734375" customWidth="1"/>
+    <col min="6" max="6" width="20.77734375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="54.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B1" s="15" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="63" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="1"/>
+      <c r="C2" s="16" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="42.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="1:5" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="44" t="s">
+        <v>90</v>
+      </c>
+      <c r="B4" s="28">
+        <v>1</v>
+      </c>
+      <c r="C4" s="29" t="s">
+        <v>86</v>
+      </c>
+      <c r="D4" s="30">
+        <v>1</v>
+      </c>
+      <c r="E4" s="31" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="45"/>
+      <c r="B5" s="32">
+        <v>2</v>
+      </c>
+      <c r="C5" s="33" t="s">
+        <v>87</v>
+      </c>
+      <c r="D5" s="34"/>
+      <c r="E5" s="35" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="45"/>
+      <c r="B6" s="32">
+        <v>3</v>
+      </c>
+      <c r="C6" s="33" t="s">
+        <v>39</v>
+      </c>
+      <c r="D6" s="34">
+        <v>1</v>
+      </c>
+      <c r="E6" s="35" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="45"/>
+      <c r="B7" s="32">
+        <v>4</v>
+      </c>
+      <c r="C7" s="33" t="s">
+        <v>27</v>
+      </c>
+      <c r="D7" s="34">
+        <v>1</v>
+      </c>
+      <c r="E7" s="36" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="45"/>
+      <c r="B8" s="32">
+        <v>5</v>
+      </c>
+      <c r="C8" s="33"/>
+      <c r="D8" s="34"/>
+      <c r="E8" s="36" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="45"/>
+      <c r="B9" s="32">
+        <v>6</v>
+      </c>
+      <c r="C9" s="34"/>
+      <c r="D9" s="34"/>
+      <c r="E9" s="35" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="45"/>
+      <c r="B10" s="32">
+        <v>7</v>
+      </c>
+      <c r="C10" s="34"/>
+      <c r="D10" s="34"/>
+      <c r="E10" s="35" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="45"/>
+      <c r="B11" s="32">
+        <v>8</v>
+      </c>
+      <c r="C11" s="34"/>
+      <c r="D11" s="34"/>
+      <c r="E11" s="35" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="45"/>
+      <c r="B12" s="32">
+        <v>9</v>
+      </c>
+      <c r="C12" s="34"/>
+      <c r="D12" s="34"/>
+      <c r="E12" s="35" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="45"/>
+      <c r="B13" s="32">
+        <v>10</v>
+      </c>
+      <c r="C13" s="34"/>
+      <c r="D13" s="34"/>
+      <c r="E13" s="35" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A14" s="45"/>
+      <c r="B14" s="32">
+        <v>11</v>
+      </c>
+      <c r="C14" s="34"/>
+      <c r="D14" s="34"/>
+      <c r="E14" s="35" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="45"/>
+      <c r="B15" s="32">
+        <v>12</v>
+      </c>
+      <c r="C15" s="34"/>
+      <c r="D15" s="34"/>
+      <c r="E15" s="35" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="45"/>
+      <c r="B16" s="32">
+        <v>13</v>
+      </c>
+      <c r="C16" s="34"/>
+      <c r="D16" s="34"/>
+      <c r="E16" s="35" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="45"/>
+      <c r="B17" s="32">
+        <v>14</v>
+      </c>
+      <c r="C17" s="34"/>
+      <c r="D17" s="34"/>
+      <c r="E17" s="35" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="45"/>
+      <c r="B18" s="32">
+        <v>15</v>
+      </c>
+      <c r="C18" s="34"/>
+      <c r="D18" s="34"/>
+      <c r="E18" s="34"/>
+    </row>
+    <row r="19" spans="1:5" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="46"/>
+      <c r="B19" s="38"/>
+      <c r="C19" s="38"/>
+      <c r="D19" s="38"/>
+      <c r="E19" s="38"/>
+    </row>
+    <row r="20" spans="1:5" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="47" t="s">
+        <v>91</v>
+      </c>
+      <c r="B20" s="32">
+        <v>1</v>
+      </c>
+      <c r="C20" s="39"/>
+      <c r="D20" s="41"/>
+      <c r="E20" s="36" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="48"/>
+      <c r="B21" s="32">
+        <v>2</v>
+      </c>
+      <c r="C21" s="37"/>
+      <c r="D21" s="41"/>
+      <c r="E21" s="36" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A22" s="48"/>
+      <c r="B22" s="32">
+        <v>3</v>
+      </c>
+      <c r="C22" s="39" t="s">
+        <v>28</v>
+      </c>
+      <c r="D22" s="41">
+        <v>1</v>
+      </c>
+      <c r="E22" s="36" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A23" s="48"/>
+      <c r="B23" s="32">
+        <v>4</v>
+      </c>
+      <c r="C23" s="39" t="s">
+        <v>38</v>
+      </c>
+      <c r="D23" s="41">
+        <v>1</v>
+      </c>
+      <c r="E23" s="36" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A24" s="48"/>
+      <c r="B24" s="32">
+        <v>5</v>
+      </c>
+      <c r="C24" s="39" t="s">
+        <v>97</v>
+      </c>
+      <c r="D24" s="41">
+        <v>1</v>
+      </c>
+      <c r="E24" s="36" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A25" s="48"/>
+      <c r="B25" s="32">
+        <v>6</v>
+      </c>
+      <c r="C25" s="39" t="s">
+        <v>34</v>
+      </c>
+      <c r="D25" s="41">
+        <v>1</v>
+      </c>
+      <c r="E25" s="36" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A26" s="48"/>
+      <c r="B26" s="32">
+        <v>7</v>
+      </c>
+      <c r="C26" s="39" t="s">
+        <v>30</v>
+      </c>
+      <c r="D26" s="41">
+        <v>1</v>
+      </c>
+      <c r="E26" s="36" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A27" s="48"/>
+      <c r="B27" s="32">
+        <v>8</v>
+      </c>
+      <c r="C27" s="39" t="s">
+        <v>26</v>
+      </c>
+      <c r="D27" s="41">
+        <v>0</v>
+      </c>
+      <c r="E27" s="36" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A28" s="48"/>
+      <c r="B28" s="32">
+        <v>9</v>
+      </c>
+      <c r="C28" s="39" t="s">
+        <v>98</v>
+      </c>
+      <c r="D28" s="41">
+        <v>0</v>
+      </c>
+      <c r="E28" s="36" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A29" s="48"/>
+      <c r="B29" s="32">
+        <v>10</v>
+      </c>
+      <c r="C29" s="39" t="s">
+        <v>63</v>
+      </c>
+      <c r="D29" s="41">
+        <v>0</v>
+      </c>
+      <c r="E29" s="36" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A30" s="48"/>
+      <c r="B30" s="32">
+        <v>11</v>
+      </c>
+      <c r="C30" s="39" t="s">
+        <v>99</v>
+      </c>
+      <c r="D30" s="41">
+        <v>1</v>
+      </c>
+      <c r="E30" s="36" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A31" s="48"/>
+      <c r="B31" s="32">
+        <v>12</v>
+      </c>
+      <c r="C31" s="39" t="s">
+        <v>31</v>
+      </c>
+      <c r="D31" s="41">
+        <v>0</v>
+      </c>
+      <c r="E31" s="36" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A32" s="48"/>
+      <c r="B32" s="32">
+        <v>13</v>
+      </c>
+      <c r="C32" s="39" t="s">
+        <v>100</v>
+      </c>
+      <c r="D32" s="41">
+        <v>1</v>
+      </c>
+      <c r="E32" s="36" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" ht="42.75" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A33" s="48"/>
+      <c r="B33" s="32">
+        <v>14</v>
+      </c>
+      <c r="C33" s="39" t="s">
+        <v>101</v>
+      </c>
+      <c r="D33" s="41">
+        <v>0</v>
+      </c>
+      <c r="E33" s="36" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A34" s="48"/>
+      <c r="B34" s="32">
+        <v>15</v>
+      </c>
+      <c r="C34" s="39" t="s">
+        <v>36</v>
+      </c>
+      <c r="D34" s="41">
+        <v>1</v>
+      </c>
+      <c r="E34" s="36" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A35" s="48"/>
+      <c r="B35" s="32">
+        <v>16</v>
+      </c>
+      <c r="C35" s="39" t="s">
+        <v>102</v>
+      </c>
+      <c r="D35" s="41">
+        <v>1</v>
+      </c>
+      <c r="E35" s="36" t="s">
+        <v>96</v>
+      </c>
+      <c r="F35" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="48"/>
+      <c r="B36" s="32">
+        <v>17</v>
+      </c>
+      <c r="C36" s="37"/>
+      <c r="D36" s="41"/>
+      <c r="E36" s="40" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="48"/>
+      <c r="B37" s="32">
+        <v>18</v>
+      </c>
+      <c r="C37" s="37"/>
+      <c r="D37" s="41"/>
+      <c r="E37" s="40" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="48"/>
+      <c r="B38" s="32">
+        <v>19</v>
+      </c>
+      <c r="C38" s="37"/>
+      <c r="D38" s="41"/>
+      <c r="E38" s="37"/>
+    </row>
+    <row r="39" spans="1:6" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="48"/>
+      <c r="B39" s="32">
+        <v>20</v>
+      </c>
+      <c r="C39" s="37"/>
+      <c r="D39" s="41"/>
+      <c r="E39" s="37"/>
+    </row>
+    <row r="40" spans="1:6" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="48"/>
+      <c r="B40" s="32">
+        <v>21</v>
+      </c>
+      <c r="C40" s="37"/>
+      <c r="D40" s="41"/>
+      <c r="E40" s="37"/>
+    </row>
+    <row r="41" spans="1:6" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="48"/>
+      <c r="B41" s="32">
+        <v>22</v>
+      </c>
+      <c r="C41" s="37"/>
+      <c r="D41" s="41"/>
+      <c r="E41" s="37"/>
+    </row>
+    <row r="42" spans="1:6" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="48"/>
+      <c r="B42" s="32">
+        <v>23</v>
+      </c>
+      <c r="C42" s="37"/>
+      <c r="D42" s="41"/>
+      <c r="E42" s="37"/>
+    </row>
+    <row r="43" spans="1:6" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="48"/>
+      <c r="B43" s="32">
+        <v>24</v>
+      </c>
+      <c r="C43" s="37"/>
+      <c r="D43" s="41"/>
+      <c r="E43" s="37"/>
+    </row>
+    <row r="44" spans="1:6" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="48"/>
+      <c r="B44" s="32">
+        <v>25</v>
+      </c>
+      <c r="C44" s="37"/>
+      <c r="D44" s="37"/>
+      <c r="E44" s="37"/>
+    </row>
+    <row r="45" spans="1:6" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="48"/>
+      <c r="B45" s="32">
+        <v>26</v>
+      </c>
+      <c r="C45" s="37"/>
+      <c r="D45" s="37"/>
+      <c r="E45" s="37"/>
+    </row>
+    <row r="46" spans="1:6" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="48"/>
+      <c r="B46" s="32">
+        <v>27</v>
+      </c>
+      <c r="C46" s="37"/>
+      <c r="D46" s="37"/>
+      <c r="E46" s="37"/>
+    </row>
+    <row r="47" spans="1:6" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="49"/>
+      <c r="B47" s="32">
+        <v>28</v>
+      </c>
+      <c r="C47" s="34"/>
+      <c r="D47" s="34"/>
+      <c r="E47" s="34"/>
+    </row>
+  </sheetData>
+  <dataConsolidate/>
+  <mergeCells count="2">
+    <mergeCell ref="A4:A19"/>
+    <mergeCell ref="A20:A47"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Enter invoicing Company Name in this cell and slogan in cell below" sqref="B1" xr:uid="{D45E2006-1F62-4B30-8B9F-0C7A965A1868}"/>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -4565,4 +5974,1700 @@
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A384F16-C35D-401C-99E2-826A16DD4F90}">
+  <dimension ref="A1:E47"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="8.88671875" customWidth="1"/>
+    <col min="2" max="2" width="8.21875" customWidth="1"/>
+    <col min="3" max="3" width="27.44140625" customWidth="1"/>
+    <col min="4" max="5" width="18.77734375" customWidth="1"/>
+    <col min="6" max="6" width="20.77734375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="54.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B1" s="15" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="63" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="1"/>
+      <c r="C2" s="16" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="42.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="1:5" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="44" t="s">
+        <v>90</v>
+      </c>
+      <c r="B4" s="28">
+        <v>1</v>
+      </c>
+      <c r="C4" s="29" t="s">
+        <v>86</v>
+      </c>
+      <c r="D4" s="30"/>
+      <c r="E4" s="31" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="45"/>
+      <c r="B5" s="32">
+        <v>2</v>
+      </c>
+      <c r="C5" s="33" t="s">
+        <v>87</v>
+      </c>
+      <c r="D5" s="34"/>
+      <c r="E5" s="35" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="45"/>
+      <c r="B6" s="32">
+        <v>3</v>
+      </c>
+      <c r="C6" s="33" t="s">
+        <v>39</v>
+      </c>
+      <c r="D6" s="34"/>
+      <c r="E6" s="35" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="45"/>
+      <c r="B7" s="32">
+        <v>4</v>
+      </c>
+      <c r="C7" s="33" t="s">
+        <v>27</v>
+      </c>
+      <c r="D7" s="34"/>
+      <c r="E7" s="36" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="45"/>
+      <c r="B8" s="32">
+        <v>5</v>
+      </c>
+      <c r="C8" s="33" t="s">
+        <v>62</v>
+      </c>
+      <c r="D8" s="34"/>
+      <c r="E8" s="36" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="45"/>
+      <c r="B9" s="32">
+        <v>6</v>
+      </c>
+      <c r="C9" s="34"/>
+      <c r="D9" s="34"/>
+      <c r="E9" s="35" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="45"/>
+      <c r="B10" s="32">
+        <v>7</v>
+      </c>
+      <c r="C10" s="34"/>
+      <c r="D10" s="34"/>
+      <c r="E10" s="35" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="45"/>
+      <c r="B11" s="32">
+        <v>8</v>
+      </c>
+      <c r="C11" s="34"/>
+      <c r="D11" s="34"/>
+      <c r="E11" s="35" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="52.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="45"/>
+      <c r="B12" s="32">
+        <v>9</v>
+      </c>
+      <c r="C12" s="34"/>
+      <c r="D12" s="34"/>
+      <c r="E12" s="35" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="45"/>
+      <c r="B13" s="32">
+        <v>10</v>
+      </c>
+      <c r="C13" s="34"/>
+      <c r="D13" s="34"/>
+      <c r="E13" s="35" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A14" s="45"/>
+      <c r="B14" s="32">
+        <v>11</v>
+      </c>
+      <c r="C14" s="34"/>
+      <c r="D14" s="34"/>
+      <c r="E14" s="35" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="45"/>
+      <c r="B15" s="32">
+        <v>12</v>
+      </c>
+      <c r="C15" s="34"/>
+      <c r="D15" s="34"/>
+      <c r="E15" s="35" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="45"/>
+      <c r="B16" s="32">
+        <v>13</v>
+      </c>
+      <c r="C16" s="34"/>
+      <c r="D16" s="34"/>
+      <c r="E16" s="35" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="45"/>
+      <c r="B17" s="32">
+        <v>14</v>
+      </c>
+      <c r="C17" s="34"/>
+      <c r="D17" s="34"/>
+      <c r="E17" s="35" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="45"/>
+      <c r="B18" s="32">
+        <v>15</v>
+      </c>
+      <c r="C18" s="34"/>
+      <c r="D18" s="34"/>
+      <c r="E18" s="34"/>
+    </row>
+    <row r="19" spans="1:5" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="46"/>
+      <c r="B19" s="38"/>
+      <c r="C19" s="38"/>
+      <c r="D19" s="38"/>
+      <c r="E19" s="38"/>
+    </row>
+    <row r="20" spans="1:5" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="47" t="s">
+        <v>91</v>
+      </c>
+      <c r="B20" s="32">
+        <v>1</v>
+      </c>
+      <c r="C20" s="39"/>
+      <c r="D20" s="41"/>
+      <c r="E20" s="36" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="48"/>
+      <c r="B21" s="32">
+        <v>2</v>
+      </c>
+      <c r="C21" s="37"/>
+      <c r="D21" s="41"/>
+      <c r="E21" s="36" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A22" s="48"/>
+      <c r="B22" s="32">
+        <v>3</v>
+      </c>
+      <c r="C22" s="39" t="s">
+        <v>28</v>
+      </c>
+      <c r="D22" s="41">
+        <v>1</v>
+      </c>
+      <c r="E22" s="36" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A23" s="48"/>
+      <c r="B23" s="32">
+        <v>4</v>
+      </c>
+      <c r="C23" s="39" t="s">
+        <v>38</v>
+      </c>
+      <c r="D23" s="41">
+        <v>1</v>
+      </c>
+      <c r="E23" s="36" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A24" s="48"/>
+      <c r="B24" s="32">
+        <v>5</v>
+      </c>
+      <c r="C24" s="39" t="s">
+        <v>97</v>
+      </c>
+      <c r="D24" s="41">
+        <v>1</v>
+      </c>
+      <c r="E24" s="36" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A25" s="48"/>
+      <c r="B25" s="32">
+        <v>6</v>
+      </c>
+      <c r="C25" s="39" t="s">
+        <v>34</v>
+      </c>
+      <c r="D25" s="41">
+        <v>1</v>
+      </c>
+      <c r="E25" s="36" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A26" s="48"/>
+      <c r="B26" s="32">
+        <v>7</v>
+      </c>
+      <c r="C26" s="39" t="s">
+        <v>30</v>
+      </c>
+      <c r="D26" s="41">
+        <v>1</v>
+      </c>
+      <c r="E26" s="36" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A27" s="48"/>
+      <c r="B27" s="32">
+        <v>8</v>
+      </c>
+      <c r="C27" s="39" t="s">
+        <v>26</v>
+      </c>
+      <c r="D27" s="41">
+        <v>1</v>
+      </c>
+      <c r="E27" s="36" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A28" s="48"/>
+      <c r="B28" s="32">
+        <v>9</v>
+      </c>
+      <c r="C28" s="39" t="s">
+        <v>98</v>
+      </c>
+      <c r="D28" s="41">
+        <v>1</v>
+      </c>
+      <c r="E28" s="36" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A29" s="48"/>
+      <c r="B29" s="32">
+        <v>10</v>
+      </c>
+      <c r="C29" s="39" t="s">
+        <v>63</v>
+      </c>
+      <c r="D29" s="41"/>
+      <c r="E29" s="36" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A30" s="48"/>
+      <c r="B30" s="32">
+        <v>11</v>
+      </c>
+      <c r="C30" s="39" t="s">
+        <v>99</v>
+      </c>
+      <c r="D30" s="41">
+        <v>1</v>
+      </c>
+      <c r="E30" s="36" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A31" s="48"/>
+      <c r="B31" s="32">
+        <v>12</v>
+      </c>
+      <c r="C31" s="39" t="s">
+        <v>31</v>
+      </c>
+      <c r="D31" s="41">
+        <v>1</v>
+      </c>
+      <c r="E31" s="36" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A32" s="48"/>
+      <c r="B32" s="32">
+        <v>13</v>
+      </c>
+      <c r="C32" s="39" t="s">
+        <v>100</v>
+      </c>
+      <c r="D32" s="41">
+        <v>1</v>
+      </c>
+      <c r="E32" s="36" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" ht="42.75" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A33" s="48"/>
+      <c r="B33" s="32">
+        <v>14</v>
+      </c>
+      <c r="C33" s="39" t="s">
+        <v>101</v>
+      </c>
+      <c r="D33" s="41">
+        <v>1</v>
+      </c>
+      <c r="E33" s="36" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A34" s="48"/>
+      <c r="B34" s="32">
+        <v>15</v>
+      </c>
+      <c r="C34" s="39" t="s">
+        <v>36</v>
+      </c>
+      <c r="D34" s="41">
+        <v>1</v>
+      </c>
+      <c r="E34" s="36" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A35" s="48"/>
+      <c r="B35" s="32">
+        <v>16</v>
+      </c>
+      <c r="C35" s="39" t="s">
+        <v>35</v>
+      </c>
+      <c r="D35" s="41">
+        <v>0</v>
+      </c>
+      <c r="E35" s="36" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="48"/>
+      <c r="B36" s="32">
+        <v>17</v>
+      </c>
+      <c r="C36" s="37"/>
+      <c r="D36" s="41"/>
+      <c r="E36" s="40" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="48"/>
+      <c r="B37" s="32">
+        <v>18</v>
+      </c>
+      <c r="C37" s="37"/>
+      <c r="D37" s="41"/>
+      <c r="E37" s="40" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="48"/>
+      <c r="B38" s="32">
+        <v>19</v>
+      </c>
+      <c r="C38" s="37"/>
+      <c r="D38" s="41"/>
+      <c r="E38" s="37"/>
+    </row>
+    <row r="39" spans="1:5" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="48"/>
+      <c r="B39" s="32">
+        <v>20</v>
+      </c>
+      <c r="C39" s="37"/>
+      <c r="D39" s="41"/>
+      <c r="E39" s="37"/>
+    </row>
+    <row r="40" spans="1:5" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="48"/>
+      <c r="B40" s="32">
+        <v>21</v>
+      </c>
+      <c r="C40" s="37"/>
+      <c r="D40" s="41"/>
+      <c r="E40" s="37"/>
+    </row>
+    <row r="41" spans="1:5" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="48"/>
+      <c r="B41" s="32">
+        <v>22</v>
+      </c>
+      <c r="C41" s="37"/>
+      <c r="D41" s="41"/>
+      <c r="E41" s="37"/>
+    </row>
+    <row r="42" spans="1:5" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="48"/>
+      <c r="B42" s="32">
+        <v>23</v>
+      </c>
+      <c r="C42" s="37"/>
+      <c r="D42" s="41"/>
+      <c r="E42" s="37"/>
+    </row>
+    <row r="43" spans="1:5" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="48"/>
+      <c r="B43" s="32">
+        <v>24</v>
+      </c>
+      <c r="C43" s="37"/>
+      <c r="D43" s="41"/>
+      <c r="E43" s="37"/>
+    </row>
+    <row r="44" spans="1:5" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="48"/>
+      <c r="B44" s="32">
+        <v>25</v>
+      </c>
+      <c r="C44" s="37"/>
+      <c r="D44" s="37"/>
+      <c r="E44" s="37"/>
+    </row>
+    <row r="45" spans="1:5" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="48"/>
+      <c r="B45" s="32">
+        <v>26</v>
+      </c>
+      <c r="C45" s="37"/>
+      <c r="D45" s="37"/>
+      <c r="E45" s="37"/>
+    </row>
+    <row r="46" spans="1:5" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="48"/>
+      <c r="B46" s="32">
+        <v>27</v>
+      </c>
+      <c r="C46" s="37"/>
+      <c r="D46" s="37"/>
+      <c r="E46" s="37"/>
+    </row>
+    <row r="47" spans="1:5" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="49"/>
+      <c r="B47" s="32">
+        <v>28</v>
+      </c>
+      <c r="C47" s="34"/>
+      <c r="D47" s="34"/>
+      <c r="E47" s="34"/>
+    </row>
+  </sheetData>
+  <dataConsolidate/>
+  <mergeCells count="2">
+    <mergeCell ref="A4:A19"/>
+    <mergeCell ref="A20:A47"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Enter invoicing Company Name in this cell and slogan in cell below" sqref="B1" xr:uid="{CEFF4535-6746-481B-806E-90166D45291B}"/>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A562E52E-0822-45EC-AA42-30657C34AA56}">
+  <dimension ref="A1:E47"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="20" customWidth="1"/>
+    <col min="2" max="2" width="8.21875" customWidth="1"/>
+    <col min="3" max="3" width="27.44140625" customWidth="1"/>
+    <col min="4" max="5" width="18.77734375" customWidth="1"/>
+    <col min="6" max="6" width="20.77734375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="54.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B1" s="15" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="63" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="1"/>
+      <c r="C2" s="16" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="42.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="1:5" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="44" t="s">
+        <v>90</v>
+      </c>
+      <c r="B4" s="28">
+        <v>1</v>
+      </c>
+      <c r="C4" s="29" t="s">
+        <v>86</v>
+      </c>
+      <c r="D4" s="30"/>
+      <c r="E4" s="31" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="45"/>
+      <c r="B5" s="32">
+        <v>2</v>
+      </c>
+      <c r="C5" s="33" t="s">
+        <v>87</v>
+      </c>
+      <c r="D5" s="34"/>
+      <c r="E5" s="35" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="45"/>
+      <c r="B6" s="32">
+        <v>3</v>
+      </c>
+      <c r="C6" s="33" t="s">
+        <v>39</v>
+      </c>
+      <c r="D6" s="34"/>
+      <c r="E6" s="35" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="45"/>
+      <c r="B7" s="32">
+        <v>4</v>
+      </c>
+      <c r="C7" s="33" t="s">
+        <v>27</v>
+      </c>
+      <c r="D7" s="34"/>
+      <c r="E7" s="36" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="45"/>
+      <c r="B8" s="32">
+        <v>5</v>
+      </c>
+      <c r="C8" s="33" t="s">
+        <v>62</v>
+      </c>
+      <c r="D8" s="34"/>
+      <c r="E8" s="36" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="45"/>
+      <c r="B9" s="32">
+        <v>6</v>
+      </c>
+      <c r="C9" s="34"/>
+      <c r="D9" s="34"/>
+      <c r="E9" s="35" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="45"/>
+      <c r="B10" s="32">
+        <v>7</v>
+      </c>
+      <c r="C10" s="34"/>
+      <c r="D10" s="34"/>
+      <c r="E10" s="35" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="45"/>
+      <c r="B11" s="32">
+        <v>8</v>
+      </c>
+      <c r="C11" s="34"/>
+      <c r="D11" s="34"/>
+      <c r="E11" s="35" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="45"/>
+      <c r="B12" s="32">
+        <v>9</v>
+      </c>
+      <c r="C12" s="34"/>
+      <c r="D12" s="34"/>
+      <c r="E12" s="35" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="45"/>
+      <c r="B13" s="32">
+        <v>10</v>
+      </c>
+      <c r="C13" s="34"/>
+      <c r="D13" s="34"/>
+      <c r="E13" s="35" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A14" s="45"/>
+      <c r="B14" s="32">
+        <v>11</v>
+      </c>
+      <c r="C14" s="34"/>
+      <c r="D14" s="34"/>
+      <c r="E14" s="35" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="45"/>
+      <c r="B15" s="32">
+        <v>12</v>
+      </c>
+      <c r="C15" s="34"/>
+      <c r="D15" s="34"/>
+      <c r="E15" s="35" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="45"/>
+      <c r="B16" s="32">
+        <v>13</v>
+      </c>
+      <c r="C16" s="34"/>
+      <c r="D16" s="34"/>
+      <c r="E16" s="35" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="45"/>
+      <c r="B17" s="32">
+        <v>14</v>
+      </c>
+      <c r="C17" s="34"/>
+      <c r="D17" s="34"/>
+      <c r="E17" s="35" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="45"/>
+      <c r="B18" s="32">
+        <v>15</v>
+      </c>
+      <c r="C18" s="34"/>
+      <c r="D18" s="34"/>
+      <c r="E18" s="34"/>
+    </row>
+    <row r="19" spans="1:5" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="46"/>
+      <c r="B19" s="38"/>
+      <c r="C19" s="38"/>
+      <c r="D19" s="38"/>
+      <c r="E19" s="38"/>
+    </row>
+    <row r="20" spans="1:5" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="47" t="s">
+        <v>91</v>
+      </c>
+      <c r="B20" s="32">
+        <v>1</v>
+      </c>
+      <c r="C20" s="39" t="s">
+        <v>102</v>
+      </c>
+      <c r="D20" s="41">
+        <v>1</v>
+      </c>
+      <c r="E20" s="36" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="48"/>
+      <c r="B21" s="32">
+        <v>2</v>
+      </c>
+      <c r="C21" s="37"/>
+      <c r="D21" s="41"/>
+      <c r="E21" s="36" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A22" s="48"/>
+      <c r="B22" s="32">
+        <v>3</v>
+      </c>
+      <c r="C22" s="39" t="s">
+        <v>28</v>
+      </c>
+      <c r="D22" s="41">
+        <v>0</v>
+      </c>
+      <c r="E22" s="36" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A23" s="48"/>
+      <c r="B23" s="32">
+        <v>4</v>
+      </c>
+      <c r="C23" s="39" t="s">
+        <v>38</v>
+      </c>
+      <c r="D23" s="41">
+        <v>1</v>
+      </c>
+      <c r="E23" s="36" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A24" s="48"/>
+      <c r="B24" s="32">
+        <v>5</v>
+      </c>
+      <c r="C24" s="39" t="s">
+        <v>97</v>
+      </c>
+      <c r="D24" s="41">
+        <v>1</v>
+      </c>
+      <c r="E24" s="36" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A25" s="48"/>
+      <c r="B25" s="32">
+        <v>6</v>
+      </c>
+      <c r="C25" s="39" t="s">
+        <v>34</v>
+      </c>
+      <c r="D25" s="41">
+        <v>1</v>
+      </c>
+      <c r="E25" s="36" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A26" s="48"/>
+      <c r="B26" s="32">
+        <v>7</v>
+      </c>
+      <c r="C26" s="39" t="s">
+        <v>30</v>
+      </c>
+      <c r="D26" s="41">
+        <v>1</v>
+      </c>
+      <c r="E26" s="36" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A27" s="48"/>
+      <c r="B27" s="32">
+        <v>8</v>
+      </c>
+      <c r="C27" s="39" t="s">
+        <v>26</v>
+      </c>
+      <c r="D27" s="41">
+        <v>1</v>
+      </c>
+      <c r="E27" s="36" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A28" s="48"/>
+      <c r="B28" s="32">
+        <v>9</v>
+      </c>
+      <c r="C28" s="39" t="s">
+        <v>98</v>
+      </c>
+      <c r="D28" s="41">
+        <v>1</v>
+      </c>
+      <c r="E28" s="36" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A29" s="48"/>
+      <c r="B29" s="32">
+        <v>10</v>
+      </c>
+      <c r="C29" s="39" t="s">
+        <v>63</v>
+      </c>
+      <c r="D29" s="41">
+        <v>1</v>
+      </c>
+      <c r="E29" s="36" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A30" s="48"/>
+      <c r="B30" s="32">
+        <v>11</v>
+      </c>
+      <c r="C30" s="39" t="s">
+        <v>99</v>
+      </c>
+      <c r="D30" s="41">
+        <v>1</v>
+      </c>
+      <c r="E30" s="36" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A31" s="48"/>
+      <c r="B31" s="32">
+        <v>12</v>
+      </c>
+      <c r="C31" s="39" t="s">
+        <v>31</v>
+      </c>
+      <c r="D31" s="41">
+        <v>1</v>
+      </c>
+      <c r="E31" s="36" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A32" s="48"/>
+      <c r="B32" s="32">
+        <v>13</v>
+      </c>
+      <c r="C32" s="39" t="s">
+        <v>100</v>
+      </c>
+      <c r="D32" s="41">
+        <v>1</v>
+      </c>
+      <c r="E32" s="36" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" ht="42.75" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A33" s="48"/>
+      <c r="B33" s="32">
+        <v>14</v>
+      </c>
+      <c r="C33" s="39" t="s">
+        <v>101</v>
+      </c>
+      <c r="D33" s="41">
+        <v>1</v>
+      </c>
+      <c r="E33" s="36" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A34" s="48"/>
+      <c r="B34" s="32">
+        <v>15</v>
+      </c>
+      <c r="C34" s="39" t="s">
+        <v>36</v>
+      </c>
+      <c r="D34" s="41">
+        <v>1</v>
+      </c>
+      <c r="E34" s="36" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A35" s="48"/>
+      <c r="B35" s="32">
+        <v>16</v>
+      </c>
+      <c r="C35" s="39"/>
+      <c r="D35" s="41"/>
+      <c r="E35" s="36" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="48"/>
+      <c r="B36" s="32">
+        <v>17</v>
+      </c>
+      <c r="C36" s="37"/>
+      <c r="D36" s="41"/>
+      <c r="E36" s="40" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="48"/>
+      <c r="B37" s="32">
+        <v>18</v>
+      </c>
+      <c r="C37" s="37"/>
+      <c r="D37" s="41"/>
+      <c r="E37" s="40" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="48"/>
+      <c r="B38" s="32">
+        <v>19</v>
+      </c>
+      <c r="C38" s="37"/>
+      <c r="D38" s="41"/>
+      <c r="E38" s="37"/>
+    </row>
+    <row r="39" spans="1:5" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="48"/>
+      <c r="B39" s="32">
+        <v>20</v>
+      </c>
+      <c r="C39" s="37"/>
+      <c r="D39" s="41"/>
+      <c r="E39" s="37"/>
+    </row>
+    <row r="40" spans="1:5" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="48"/>
+      <c r="B40" s="32">
+        <v>21</v>
+      </c>
+      <c r="C40" s="37"/>
+      <c r="D40" s="41"/>
+      <c r="E40" s="37"/>
+    </row>
+    <row r="41" spans="1:5" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="48"/>
+      <c r="B41" s="32">
+        <v>22</v>
+      </c>
+      <c r="C41" s="37"/>
+      <c r="D41" s="41"/>
+      <c r="E41" s="37"/>
+    </row>
+    <row r="42" spans="1:5" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="48"/>
+      <c r="B42" s="32">
+        <v>23</v>
+      </c>
+      <c r="C42" s="37"/>
+      <c r="D42" s="41"/>
+      <c r="E42" s="37"/>
+    </row>
+    <row r="43" spans="1:5" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="48"/>
+      <c r="B43" s="32">
+        <v>24</v>
+      </c>
+      <c r="C43" s="37"/>
+      <c r="D43" s="41"/>
+      <c r="E43" s="37"/>
+    </row>
+    <row r="44" spans="1:5" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="48"/>
+      <c r="B44" s="32">
+        <v>25</v>
+      </c>
+      <c r="C44" s="37"/>
+      <c r="D44" s="37"/>
+      <c r="E44" s="37"/>
+    </row>
+    <row r="45" spans="1:5" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="48"/>
+      <c r="B45" s="32">
+        <v>26</v>
+      </c>
+      <c r="C45" s="37"/>
+      <c r="D45" s="37"/>
+      <c r="E45" s="37"/>
+    </row>
+    <row r="46" spans="1:5" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="48"/>
+      <c r="B46" s="32">
+        <v>27</v>
+      </c>
+      <c r="C46" s="37"/>
+      <c r="D46" s="37"/>
+      <c r="E46" s="37"/>
+    </row>
+    <row r="47" spans="1:5" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="49"/>
+      <c r="B47" s="32">
+        <v>28</v>
+      </c>
+      <c r="C47" s="34"/>
+      <c r="D47" s="34"/>
+      <c r="E47" s="34"/>
+    </row>
+  </sheetData>
+  <dataConsolidate/>
+  <mergeCells count="2">
+    <mergeCell ref="A4:A19"/>
+    <mergeCell ref="A20:A47"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Enter invoicing Company Name in this cell and slogan in cell below" sqref="B1" xr:uid="{68B43A9C-C5D3-4EEA-AB4A-3BC4C4EEBE32}"/>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F5D0ECA-317E-43C4-BF3B-1CB63803CBA3}">
+  <dimension ref="A1:E47"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="20" customWidth="1"/>
+    <col min="2" max="2" width="8.21875" customWidth="1"/>
+    <col min="3" max="3" width="27.44140625" customWidth="1"/>
+    <col min="4" max="5" width="18.77734375" customWidth="1"/>
+    <col min="6" max="6" width="20.77734375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="54.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B1" s="15" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="63" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="1"/>
+      <c r="C2" s="16" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="42.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="1:5" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="44" t="s">
+        <v>90</v>
+      </c>
+      <c r="B4" s="28">
+        <v>1</v>
+      </c>
+      <c r="C4" s="29" t="s">
+        <v>86</v>
+      </c>
+      <c r="D4" s="30"/>
+      <c r="E4" s="31" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="45"/>
+      <c r="B5" s="32">
+        <v>2</v>
+      </c>
+      <c r="C5" s="33" t="s">
+        <v>87</v>
+      </c>
+      <c r="D5" s="34"/>
+      <c r="E5" s="35" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="45"/>
+      <c r="B6" s="32">
+        <v>3</v>
+      </c>
+      <c r="C6" s="33" t="s">
+        <v>39</v>
+      </c>
+      <c r="D6" s="34"/>
+      <c r="E6" s="35" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="45"/>
+      <c r="B7" s="32">
+        <v>4</v>
+      </c>
+      <c r="C7" s="33" t="s">
+        <v>27</v>
+      </c>
+      <c r="D7" s="34"/>
+      <c r="E7" s="36" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="45"/>
+      <c r="B8" s="32">
+        <v>5</v>
+      </c>
+      <c r="C8" s="33" t="s">
+        <v>62</v>
+      </c>
+      <c r="D8" s="34"/>
+      <c r="E8" s="36" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="45"/>
+      <c r="B9" s="32">
+        <v>6</v>
+      </c>
+      <c r="C9" s="34"/>
+      <c r="D9" s="34"/>
+      <c r="E9" s="35" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="45"/>
+      <c r="B10" s="32">
+        <v>7</v>
+      </c>
+      <c r="C10" s="34"/>
+      <c r="D10" s="34"/>
+      <c r="E10" s="35" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="45"/>
+      <c r="B11" s="32">
+        <v>8</v>
+      </c>
+      <c r="C11" s="34"/>
+      <c r="D11" s="34"/>
+      <c r="E11" s="35" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="45"/>
+      <c r="B12" s="32">
+        <v>9</v>
+      </c>
+      <c r="C12" s="34"/>
+      <c r="D12" s="34"/>
+      <c r="E12" s="35" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="45"/>
+      <c r="B13" s="32">
+        <v>10</v>
+      </c>
+      <c r="C13" s="34"/>
+      <c r="D13" s="34"/>
+      <c r="E13" s="35" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A14" s="45"/>
+      <c r="B14" s="32">
+        <v>11</v>
+      </c>
+      <c r="C14" s="34"/>
+      <c r="D14" s="34"/>
+      <c r="E14" s="35" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="45"/>
+      <c r="B15" s="32">
+        <v>12</v>
+      </c>
+      <c r="C15" s="34"/>
+      <c r="D15" s="34"/>
+      <c r="E15" s="35" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="45"/>
+      <c r="B16" s="32">
+        <v>13</v>
+      </c>
+      <c r="C16" s="34"/>
+      <c r="D16" s="34"/>
+      <c r="E16" s="35" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="45"/>
+      <c r="B17" s="32">
+        <v>14</v>
+      </c>
+      <c r="C17" s="34"/>
+      <c r="D17" s="34"/>
+      <c r="E17" s="35" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="45"/>
+      <c r="B18" s="32">
+        <v>15</v>
+      </c>
+      <c r="C18" s="34"/>
+      <c r="D18" s="34"/>
+      <c r="E18" s="34"/>
+    </row>
+    <row r="19" spans="1:5" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="46"/>
+      <c r="B19" s="38"/>
+      <c r="C19" s="38"/>
+      <c r="D19" s="38"/>
+      <c r="E19" s="38"/>
+    </row>
+    <row r="20" spans="1:5" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="47" t="s">
+        <v>91</v>
+      </c>
+      <c r="B20" s="32">
+        <v>1</v>
+      </c>
+      <c r="C20" s="39" t="s">
+        <v>102</v>
+      </c>
+      <c r="D20" s="41">
+        <v>0</v>
+      </c>
+      <c r="E20" s="36" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="48"/>
+      <c r="B21" s="32">
+        <v>2</v>
+      </c>
+      <c r="C21" s="37"/>
+      <c r="D21" s="41"/>
+      <c r="E21" s="36" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A22" s="48"/>
+      <c r="B22" s="32">
+        <v>3</v>
+      </c>
+      <c r="C22" s="39" t="s">
+        <v>28</v>
+      </c>
+      <c r="D22" s="41">
+        <v>0</v>
+      </c>
+      <c r="E22" s="36" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A23" s="48"/>
+      <c r="B23" s="32">
+        <v>4</v>
+      </c>
+      <c r="C23" s="39" t="s">
+        <v>38</v>
+      </c>
+      <c r="D23" s="41">
+        <v>1</v>
+      </c>
+      <c r="E23" s="36" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A24" s="48"/>
+      <c r="B24" s="32">
+        <v>5</v>
+      </c>
+      <c r="C24" s="39" t="s">
+        <v>97</v>
+      </c>
+      <c r="D24" s="41">
+        <v>1</v>
+      </c>
+      <c r="E24" s="36" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A25" s="48"/>
+      <c r="B25" s="32">
+        <v>6</v>
+      </c>
+      <c r="C25" s="39" t="s">
+        <v>34</v>
+      </c>
+      <c r="D25" s="41">
+        <v>1</v>
+      </c>
+      <c r="E25" s="36" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A26" s="48"/>
+      <c r="B26" s="32">
+        <v>7</v>
+      </c>
+      <c r="C26" s="39" t="s">
+        <v>30</v>
+      </c>
+      <c r="D26" s="41">
+        <v>1</v>
+      </c>
+      <c r="E26" s="36" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A27" s="48"/>
+      <c r="B27" s="32">
+        <v>8</v>
+      </c>
+      <c r="C27" s="39" t="s">
+        <v>26</v>
+      </c>
+      <c r="D27" s="41">
+        <v>1</v>
+      </c>
+      <c r="E27" s="36" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A28" s="48"/>
+      <c r="B28" s="32">
+        <v>9</v>
+      </c>
+      <c r="C28" s="39" t="s">
+        <v>98</v>
+      </c>
+      <c r="D28" s="41">
+        <v>1</v>
+      </c>
+      <c r="E28" s="36" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A29" s="48"/>
+      <c r="B29" s="32">
+        <v>10</v>
+      </c>
+      <c r="C29" s="39" t="s">
+        <v>63</v>
+      </c>
+      <c r="D29" s="41">
+        <v>0</v>
+      </c>
+      <c r="E29" s="36" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A30" s="48"/>
+      <c r="B30" s="32">
+        <v>11</v>
+      </c>
+      <c r="C30" s="39" t="s">
+        <v>99</v>
+      </c>
+      <c r="D30" s="41">
+        <v>1</v>
+      </c>
+      <c r="E30" s="36" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A31" s="48"/>
+      <c r="B31" s="32">
+        <v>12</v>
+      </c>
+      <c r="C31" s="39" t="s">
+        <v>31</v>
+      </c>
+      <c r="D31" s="41">
+        <v>1</v>
+      </c>
+      <c r="E31" s="36" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A32" s="48"/>
+      <c r="B32" s="32">
+        <v>13</v>
+      </c>
+      <c r="C32" s="39" t="s">
+        <v>100</v>
+      </c>
+      <c r="D32" s="41">
+        <v>1</v>
+      </c>
+      <c r="E32" s="36" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" ht="42.75" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A33" s="48"/>
+      <c r="B33" s="32">
+        <v>14</v>
+      </c>
+      <c r="C33" s="39" t="s">
+        <v>101</v>
+      </c>
+      <c r="D33" s="41">
+        <v>1</v>
+      </c>
+      <c r="E33" s="36" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A34" s="48"/>
+      <c r="B34" s="32">
+        <v>15</v>
+      </c>
+      <c r="C34" s="39" t="s">
+        <v>36</v>
+      </c>
+      <c r="D34" s="41">
+        <v>1</v>
+      </c>
+      <c r="E34" s="36" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A35" s="48"/>
+      <c r="B35" s="32">
+        <v>16</v>
+      </c>
+      <c r="C35" s="39"/>
+      <c r="D35" s="41"/>
+      <c r="E35" s="36" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="48"/>
+      <c r="B36" s="32">
+        <v>17</v>
+      </c>
+      <c r="C36" s="37"/>
+      <c r="D36" s="41"/>
+      <c r="E36" s="40" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="48"/>
+      <c r="B37" s="32">
+        <v>18</v>
+      </c>
+      <c r="C37" s="37"/>
+      <c r="D37" s="41"/>
+      <c r="E37" s="40" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="48"/>
+      <c r="B38" s="32">
+        <v>19</v>
+      </c>
+      <c r="C38" s="37"/>
+      <c r="D38" s="41"/>
+      <c r="E38" s="37"/>
+    </row>
+    <row r="39" spans="1:5" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="48"/>
+      <c r="B39" s="32">
+        <v>20</v>
+      </c>
+      <c r="C39" s="37"/>
+      <c r="D39" s="41"/>
+      <c r="E39" s="37"/>
+    </row>
+    <row r="40" spans="1:5" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="48"/>
+      <c r="B40" s="32">
+        <v>21</v>
+      </c>
+      <c r="C40" s="37"/>
+      <c r="D40" s="41"/>
+      <c r="E40" s="37"/>
+    </row>
+    <row r="41" spans="1:5" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="48"/>
+      <c r="B41" s="32">
+        <v>22</v>
+      </c>
+      <c r="C41" s="37"/>
+      <c r="D41" s="41"/>
+      <c r="E41" s="37"/>
+    </row>
+    <row r="42" spans="1:5" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="48"/>
+      <c r="B42" s="32">
+        <v>23</v>
+      </c>
+      <c r="C42" s="37"/>
+      <c r="D42" s="41"/>
+      <c r="E42" s="37"/>
+    </row>
+    <row r="43" spans="1:5" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="48"/>
+      <c r="B43" s="32">
+        <v>24</v>
+      </c>
+      <c r="C43" s="37"/>
+      <c r="D43" s="41"/>
+      <c r="E43" s="37"/>
+    </row>
+    <row r="44" spans="1:5" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="48"/>
+      <c r="B44" s="32">
+        <v>25</v>
+      </c>
+      <c r="C44" s="37"/>
+      <c r="D44" s="37"/>
+      <c r="E44" s="37"/>
+    </row>
+    <row r="45" spans="1:5" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="48"/>
+      <c r="B45" s="32">
+        <v>26</v>
+      </c>
+      <c r="C45" s="37"/>
+      <c r="D45" s="37"/>
+      <c r="E45" s="37"/>
+    </row>
+    <row r="46" spans="1:5" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="48"/>
+      <c r="B46" s="32">
+        <v>27</v>
+      </c>
+      <c r="C46" s="37"/>
+      <c r="D46" s="37"/>
+      <c r="E46" s="37"/>
+    </row>
+    <row r="47" spans="1:5" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="49"/>
+      <c r="B47" s="32">
+        <v>28</v>
+      </c>
+      <c r="C47" s="34"/>
+      <c r="D47" s="34"/>
+      <c r="E47" s="34"/>
+    </row>
+  </sheetData>
+  <dataConsolidate/>
+  <mergeCells count="2">
+    <mergeCell ref="A4:A19"/>
+    <mergeCell ref="A20:A47"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Enter invoicing Company Name in this cell and slogan in cell below" sqref="B1" xr:uid="{D0EC6DDF-69F5-44E1-B007-AFA8894D9BAE}"/>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>
--- a/Chấm công/ĐIÊM DANH T3.xlsx
+++ b/Chấm công/ĐIÊM DANH T3.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Duc Anh\Chấm công\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6192D05-B39D-45D8-AE27-EDE3AB77076D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6230F78-A2AA-4DD4-99C9-1D1A11FB79FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="10" xr2:uid="{5F25DB95-9F61-4E14-A6AC-3108B48F6C7D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="13" xr2:uid="{5F25DB95-9F61-4E14-A6AC-3108B48F6C7D}"/>
   </bookViews>
   <sheets>
     <sheet name="DANH SÁCH XE" sheetId="6" r:id="rId1"/>
@@ -24,6 +24,9 @@
     <sheet name="25-03" sheetId="9" r:id="rId9"/>
     <sheet name="26-03." sheetId="10" r:id="rId10"/>
     <sheet name="27-03" sheetId="11" r:id="rId11"/>
+    <sheet name="28-03" sheetId="12" r:id="rId12"/>
+    <sheet name="29-03" sheetId="13" r:id="rId13"/>
+    <sheet name="Sheet1" sheetId="14" r:id="rId14"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -44,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="905" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1051" uniqueCount="113">
   <si>
     <t>HỌ TÊN</t>
   </si>
@@ -356,13 +359,40 @@
   </si>
   <si>
     <t>lấy xe của lập chạy</t>
+  </si>
+  <si>
+    <t>MAI NGỌC VĂN</t>
+  </si>
+  <si>
+    <t>HUỲNH THANH PHONG</t>
+  </si>
+  <si>
+    <t>XE BỊ XÍCH SUN</t>
+  </si>
+  <si>
+    <t>XE BỊ XÍCH VIN</t>
+  </si>
+  <si>
+    <t>Tên</t>
+  </si>
+  <si>
+    <t>Có đi làm</t>
+  </si>
+  <si>
+    <t>Biển Số</t>
+  </si>
+  <si>
+    <t>Ghi chú</t>
+  </si>
+  <si>
+    <t>Xe bị xích SUN</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="13"/>
       <color theme="1"/>
@@ -458,6 +488,13 @@
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
   </fonts>
   <fills count="11">
@@ -672,7 +709,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -793,6 +830,12 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -816,6 +859,33 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1671,7 +1741,7 @@
       </c>
     </row>
     <row r="34" spans="1:7" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A34" s="42" t="s">
+      <c r="A34" s="44" t="s">
         <v>90</v>
       </c>
       <c r="B34" s="26">
@@ -1688,7 +1758,7 @@
       <c r="G34" s="11"/>
     </row>
     <row r="35" spans="1:7" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A35" s="42"/>
+      <c r="A35" s="44"/>
       <c r="B35" s="26">
         <f>B34+1</f>
         <v>2</v>
@@ -1706,7 +1776,7 @@
       <c r="G35" s="11"/>
     </row>
     <row r="36" spans="1:7" ht="23.25" x14ac:dyDescent="0.35">
-      <c r="A36" s="42"/>
+      <c r="A36" s="44"/>
       <c r="B36" s="26">
         <f t="shared" ref="B36:B68" si="1">B35+1</f>
         <v>3</v>
@@ -1722,7 +1792,7 @@
       <c r="G36" s="11"/>
     </row>
     <row r="37" spans="1:7" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A37" s="42"/>
+      <c r="A37" s="44"/>
       <c r="B37" s="26">
         <f t="shared" si="1"/>
         <v>4</v>
@@ -1740,7 +1810,7 @@
       <c r="G37" s="11"/>
     </row>
     <row r="38" spans="1:7" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A38" s="42"/>
+      <c r="A38" s="44"/>
       <c r="B38" s="26">
         <f t="shared" si="1"/>
         <v>5</v>
@@ -1754,7 +1824,7 @@
       <c r="G38" s="11"/>
     </row>
     <row r="39" spans="1:7" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A39" s="42"/>
+      <c r="A39" s="44"/>
       <c r="B39" s="26">
         <f t="shared" si="1"/>
         <v>6</v>
@@ -1770,7 +1840,7 @@
       <c r="G39" s="11"/>
     </row>
     <row r="40" spans="1:7" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A40" s="42"/>
+      <c r="A40" s="44"/>
       <c r="B40" s="26">
         <f t="shared" si="1"/>
         <v>7</v>
@@ -1786,7 +1856,7 @@
       <c r="G40" s="11"/>
     </row>
     <row r="41" spans="1:7" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A41" s="42"/>
+      <c r="A41" s="44"/>
       <c r="B41" s="26">
         <f t="shared" si="1"/>
         <v>8</v>
@@ -1802,7 +1872,7 @@
       <c r="G41" s="11"/>
     </row>
     <row r="42" spans="1:7" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A42" s="42"/>
+      <c r="A42" s="44"/>
       <c r="B42" s="26">
         <f t="shared" si="1"/>
         <v>9</v>
@@ -1820,7 +1890,7 @@
       <c r="G42" s="11"/>
     </row>
     <row r="43" spans="1:7" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A43" s="42"/>
+      <c r="A43" s="44"/>
       <c r="B43" s="26">
         <f t="shared" si="1"/>
         <v>10</v>
@@ -1836,7 +1906,7 @@
       <c r="G43" s="11"/>
     </row>
     <row r="44" spans="1:7" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A44" s="42"/>
+      <c r="A44" s="44"/>
       <c r="B44" s="26">
         <f t="shared" si="1"/>
         <v>11</v>
@@ -1854,7 +1924,7 @@
       <c r="G44" s="11"/>
     </row>
     <row r="45" spans="1:7" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A45" s="42"/>
+      <c r="A45" s="44"/>
       <c r="B45" s="26">
         <f t="shared" si="1"/>
         <v>12</v>
@@ -1872,7 +1942,7 @@
       <c r="G45" s="11"/>
     </row>
     <row r="46" spans="1:7" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A46" s="42"/>
+      <c r="A46" s="44"/>
       <c r="B46" s="26">
         <f t="shared" si="1"/>
         <v>13</v>
@@ -1888,7 +1958,7 @@
       <c r="G46" s="11"/>
     </row>
     <row r="47" spans="1:7" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A47" s="42"/>
+      <c r="A47" s="44"/>
       <c r="B47" s="26">
         <f t="shared" si="1"/>
         <v>14</v>
@@ -1904,7 +1974,7 @@
       <c r="G47" s="11"/>
     </row>
     <row r="48" spans="1:7" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A48" s="43" t="s">
+      <c r="A48" s="45" t="s">
         <v>91</v>
       </c>
       <c r="B48" s="27">
@@ -1919,7 +1989,7 @@
       <c r="G48" s="11"/>
     </row>
     <row r="49" spans="1:7" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A49" s="43"/>
+      <c r="A49" s="45"/>
       <c r="B49" s="27">
         <f>B48+1</f>
         <v>2</v>
@@ -1935,7 +2005,7 @@
       <c r="G49" s="11"/>
     </row>
     <row r="50" spans="1:7" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A50" s="43"/>
+      <c r="A50" s="45"/>
       <c r="B50" s="27">
         <f t="shared" si="1"/>
         <v>3</v>
@@ -1949,7 +2019,7 @@
       <c r="G50" s="11"/>
     </row>
     <row r="51" spans="1:7" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A51" s="43"/>
+      <c r="A51" s="45"/>
       <c r="B51" s="27">
         <f t="shared" si="1"/>
         <v>4</v>
@@ -1965,7 +2035,7 @@
       <c r="G51" s="11"/>
     </row>
     <row r="52" spans="1:7" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A52" s="43"/>
+      <c r="A52" s="45"/>
       <c r="B52" s="27">
         <f t="shared" si="1"/>
         <v>5</v>
@@ -1981,7 +2051,7 @@
       <c r="G52" s="11"/>
     </row>
     <row r="53" spans="1:7" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A53" s="43"/>
+      <c r="A53" s="45"/>
       <c r="B53" s="27">
         <f t="shared" si="1"/>
         <v>6</v>
@@ -1997,7 +2067,7 @@
       <c r="G53" s="11"/>
     </row>
     <row r="54" spans="1:7" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A54" s="43"/>
+      <c r="A54" s="45"/>
       <c r="B54" s="27">
         <f t="shared" si="1"/>
         <v>7</v>
@@ -2013,7 +2083,7 @@
       <c r="G54" s="13"/>
     </row>
     <row r="55" spans="1:7" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A55" s="43"/>
+      <c r="A55" s="45"/>
       <c r="B55" s="27">
         <f t="shared" si="1"/>
         <v>8</v>
@@ -2029,7 +2099,7 @@
       <c r="G55" s="11"/>
     </row>
     <row r="56" spans="1:7" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A56" s="43"/>
+      <c r="A56" s="45"/>
       <c r="B56" s="27">
         <f t="shared" si="1"/>
         <v>9</v>
@@ -2045,7 +2115,7 @@
       <c r="G56" s="11"/>
     </row>
     <row r="57" spans="1:7" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A57" s="43"/>
+      <c r="A57" s="45"/>
       <c r="B57" s="27">
         <f t="shared" si="1"/>
         <v>10</v>
@@ -2059,7 +2129,7 @@
       <c r="G57" s="11"/>
     </row>
     <row r="58" spans="1:7" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A58" s="43"/>
+      <c r="A58" s="45"/>
       <c r="B58" s="27">
         <f t="shared" si="1"/>
         <v>11</v>
@@ -2073,7 +2143,7 @@
       <c r="G58" s="11"/>
     </row>
     <row r="59" spans="1:7" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A59" s="43"/>
+      <c r="A59" s="45"/>
       <c r="B59" s="27">
         <f t="shared" si="1"/>
         <v>12</v>
@@ -2087,7 +2157,7 @@
       <c r="G59" s="11"/>
     </row>
     <row r="60" spans="1:7" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A60" s="43"/>
+      <c r="A60" s="45"/>
       <c r="B60" s="27">
         <f t="shared" si="1"/>
         <v>13</v>
@@ -2101,7 +2171,7 @@
       <c r="G60" s="11"/>
     </row>
     <row r="61" spans="1:7" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A61" s="43"/>
+      <c r="A61" s="45"/>
       <c r="B61" s="27">
         <f t="shared" si="1"/>
         <v>14</v>
@@ -2115,7 +2185,7 @@
       <c r="G61" s="11"/>
     </row>
     <row r="62" spans="1:7" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A62" s="43"/>
+      <c r="A62" s="45"/>
       <c r="B62" s="27">
         <f t="shared" si="1"/>
         <v>15</v>
@@ -2129,7 +2199,7 @@
       <c r="G62" s="11"/>
     </row>
     <row r="63" spans="1:7" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A63" s="43"/>
+      <c r="A63" s="45"/>
       <c r="B63" s="27">
         <f t="shared" si="1"/>
         <v>16</v>
@@ -2143,7 +2213,7 @@
       <c r="G63" s="11"/>
     </row>
     <row r="64" spans="1:7" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A64" s="43"/>
+      <c r="A64" s="45"/>
       <c r="B64" s="27">
         <f t="shared" si="1"/>
         <v>17</v>
@@ -2155,7 +2225,7 @@
       <c r="G64" s="11"/>
     </row>
     <row r="65" spans="1:7" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A65" s="43"/>
+      <c r="A65" s="45"/>
       <c r="B65" s="27">
         <f t="shared" si="1"/>
         <v>18</v>
@@ -2167,7 +2237,7 @@
       <c r="G65" s="11"/>
     </row>
     <row r="66" spans="1:7" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A66" s="43"/>
+      <c r="A66" s="45"/>
       <c r="B66" s="27">
         <f t="shared" si="1"/>
         <v>19</v>
@@ -2179,7 +2249,7 @@
       <c r="G66" s="11"/>
     </row>
     <row r="67" spans="1:7" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A67" s="43"/>
+      <c r="A67" s="45"/>
       <c r="B67" s="27">
         <f t="shared" si="1"/>
         <v>20</v>
@@ -2191,7 +2261,7 @@
       <c r="G67" s="11"/>
     </row>
     <row r="68" spans="1:7" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A68" s="43"/>
+      <c r="A68" s="45"/>
       <c r="B68" s="27">
         <f t="shared" si="1"/>
         <v>21</v>
@@ -2244,7 +2314,7 @@
     </row>
     <row r="3" spans="1:5" ht="42.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:5" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="44" t="s">
+      <c r="A4" s="46" t="s">
         <v>90</v>
       </c>
       <c r="B4" s="28">
@@ -2261,7 +2331,7 @@
       </c>
     </row>
     <row r="5" spans="1:5" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="45"/>
+      <c r="A5" s="47"/>
       <c r="B5" s="32">
         <v>2</v>
       </c>
@@ -2274,7 +2344,7 @@
       </c>
     </row>
     <row r="6" spans="1:5" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="45"/>
+      <c r="A6" s="47"/>
       <c r="B6" s="32">
         <v>3</v>
       </c>
@@ -2289,7 +2359,7 @@
       </c>
     </row>
     <row r="7" spans="1:5" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="45"/>
+      <c r="A7" s="47"/>
       <c r="B7" s="32">
         <v>4</v>
       </c>
@@ -2304,7 +2374,7 @@
       </c>
     </row>
     <row r="8" spans="1:5" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="45"/>
+      <c r="A8" s="47"/>
       <c r="B8" s="32">
         <v>5</v>
       </c>
@@ -2315,7 +2385,7 @@
       </c>
     </row>
     <row r="9" spans="1:5" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="45"/>
+      <c r="A9" s="47"/>
       <c r="B9" s="32">
         <v>6</v>
       </c>
@@ -2326,7 +2396,7 @@
       </c>
     </row>
     <row r="10" spans="1:5" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="45"/>
+      <c r="A10" s="47"/>
       <c r="B10" s="32">
         <v>7</v>
       </c>
@@ -2337,7 +2407,7 @@
       </c>
     </row>
     <row r="11" spans="1:5" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="45"/>
+      <c r="A11" s="47"/>
       <c r="B11" s="32">
         <v>8</v>
       </c>
@@ -2348,7 +2418,7 @@
       </c>
     </row>
     <row r="12" spans="1:5" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="45"/>
+      <c r="A12" s="47"/>
       <c r="B12" s="32">
         <v>9</v>
       </c>
@@ -2359,7 +2429,7 @@
       </c>
     </row>
     <row r="13" spans="1:5" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="45"/>
+      <c r="A13" s="47"/>
       <c r="B13" s="32">
         <v>10</v>
       </c>
@@ -2370,7 +2440,7 @@
       </c>
     </row>
     <row r="14" spans="1:5" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="45"/>
+      <c r="A14" s="47"/>
       <c r="B14" s="32">
         <v>11</v>
       </c>
@@ -2381,7 +2451,7 @@
       </c>
     </row>
     <row r="15" spans="1:5" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="45"/>
+      <c r="A15" s="47"/>
       <c r="B15" s="32">
         <v>12</v>
       </c>
@@ -2392,7 +2462,7 @@
       </c>
     </row>
     <row r="16" spans="1:5" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="45"/>
+      <c r="A16" s="47"/>
       <c r="B16" s="32">
         <v>13</v>
       </c>
@@ -2403,7 +2473,7 @@
       </c>
     </row>
     <row r="17" spans="1:5" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="45"/>
+      <c r="A17" s="47"/>
       <c r="B17" s="32">
         <v>14</v>
       </c>
@@ -2414,7 +2484,7 @@
       </c>
     </row>
     <row r="18" spans="1:5" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="45"/>
+      <c r="A18" s="47"/>
       <c r="B18" s="32">
         <v>15</v>
       </c>
@@ -2423,14 +2493,14 @@
       <c r="E18" s="34"/>
     </row>
     <row r="19" spans="1:5" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="46"/>
+      <c r="A19" s="48"/>
       <c r="B19" s="38"/>
       <c r="C19" s="38"/>
       <c r="D19" s="38"/>
       <c r="E19" s="38"/>
     </row>
     <row r="20" spans="1:5" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="47" t="s">
+      <c r="A20" s="49" t="s">
         <v>91</v>
       </c>
       <c r="B20" s="32">
@@ -2443,7 +2513,7 @@
       </c>
     </row>
     <row r="21" spans="1:5" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="48"/>
+      <c r="A21" s="50"/>
       <c r="B21" s="32">
         <v>2</v>
       </c>
@@ -2454,7 +2524,7 @@
       </c>
     </row>
     <row r="22" spans="1:5" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="48"/>
+      <c r="A22" s="50"/>
       <c r="B22" s="32">
         <v>3</v>
       </c>
@@ -2469,7 +2539,7 @@
       </c>
     </row>
     <row r="23" spans="1:5" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="48"/>
+      <c r="A23" s="50"/>
       <c r="B23" s="32">
         <v>4</v>
       </c>
@@ -2484,7 +2554,7 @@
       </c>
     </row>
     <row r="24" spans="1:5" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="48"/>
+      <c r="A24" s="50"/>
       <c r="B24" s="32">
         <v>5</v>
       </c>
@@ -2499,7 +2569,7 @@
       </c>
     </row>
     <row r="25" spans="1:5" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="48"/>
+      <c r="A25" s="50"/>
       <c r="B25" s="32">
         <v>6</v>
       </c>
@@ -2514,7 +2584,7 @@
       </c>
     </row>
     <row r="26" spans="1:5" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="48"/>
+      <c r="A26" s="50"/>
       <c r="B26" s="32">
         <v>7</v>
       </c>
@@ -2529,7 +2599,7 @@
       </c>
     </row>
     <row r="27" spans="1:5" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="48"/>
+      <c r="A27" s="50"/>
       <c r="B27" s="32">
         <v>8</v>
       </c>
@@ -2544,7 +2614,7 @@
       </c>
     </row>
     <row r="28" spans="1:5" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="48"/>
+      <c r="A28" s="50"/>
       <c r="B28" s="32">
         <v>9</v>
       </c>
@@ -2559,7 +2629,7 @@
       </c>
     </row>
     <row r="29" spans="1:5" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A29" s="48"/>
+      <c r="A29" s="50"/>
       <c r="B29" s="32">
         <v>10</v>
       </c>
@@ -2574,7 +2644,7 @@
       </c>
     </row>
     <row r="30" spans="1:5" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A30" s="48"/>
+      <c r="A30" s="50"/>
       <c r="B30" s="32">
         <v>11</v>
       </c>
@@ -2589,7 +2659,7 @@
       </c>
     </row>
     <row r="31" spans="1:5" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A31" s="48"/>
+      <c r="A31" s="50"/>
       <c r="B31" s="32">
         <v>12</v>
       </c>
@@ -2604,7 +2674,7 @@
       </c>
     </row>
     <row r="32" spans="1:5" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A32" s="48"/>
+      <c r="A32" s="50"/>
       <c r="B32" s="32">
         <v>13</v>
       </c>
@@ -2619,7 +2689,7 @@
       </c>
     </row>
     <row r="33" spans="1:5" ht="42.75" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A33" s="48"/>
+      <c r="A33" s="50"/>
       <c r="B33" s="32">
         <v>14</v>
       </c>
@@ -2634,7 +2704,7 @@
       </c>
     </row>
     <row r="34" spans="1:5" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A34" s="48"/>
+      <c r="A34" s="50"/>
       <c r="B34" s="32">
         <v>15</v>
       </c>
@@ -2649,7 +2719,7 @@
       </c>
     </row>
     <row r="35" spans="1:5" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A35" s="48"/>
+      <c r="A35" s="50"/>
       <c r="B35" s="32">
         <v>16</v>
       </c>
@@ -2664,7 +2734,7 @@
       </c>
     </row>
     <row r="36" spans="1:5" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="48"/>
+      <c r="A36" s="50"/>
       <c r="B36" s="32">
         <v>17</v>
       </c>
@@ -2675,7 +2745,7 @@
       </c>
     </row>
     <row r="37" spans="1:5" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="48"/>
+      <c r="A37" s="50"/>
       <c r="B37" s="32">
         <v>18</v>
       </c>
@@ -2686,7 +2756,7 @@
       </c>
     </row>
     <row r="38" spans="1:5" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="48"/>
+      <c r="A38" s="50"/>
       <c r="B38" s="32">
         <v>19</v>
       </c>
@@ -2695,7 +2765,7 @@
       <c r="E38" s="37"/>
     </row>
     <row r="39" spans="1:5" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="48"/>
+      <c r="A39" s="50"/>
       <c r="B39" s="32">
         <v>20</v>
       </c>
@@ -2704,7 +2774,7 @@
       <c r="E39" s="37"/>
     </row>
     <row r="40" spans="1:5" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="48"/>
+      <c r="A40" s="50"/>
       <c r="B40" s="32">
         <v>21</v>
       </c>
@@ -2713,7 +2783,7 @@
       <c r="E40" s="37"/>
     </row>
     <row r="41" spans="1:5" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="48"/>
+      <c r="A41" s="50"/>
       <c r="B41" s="32">
         <v>22</v>
       </c>
@@ -2722,7 +2792,7 @@
       <c r="E41" s="37"/>
     </row>
     <row r="42" spans="1:5" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="48"/>
+      <c r="A42" s="50"/>
       <c r="B42" s="32">
         <v>23</v>
       </c>
@@ -2731,7 +2801,7 @@
       <c r="E42" s="37"/>
     </row>
     <row r="43" spans="1:5" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="48"/>
+      <c r="A43" s="50"/>
       <c r="B43" s="32">
         <v>24</v>
       </c>
@@ -2740,7 +2810,7 @@
       <c r="E43" s="37"/>
     </row>
     <row r="44" spans="1:5" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="48"/>
+      <c r="A44" s="50"/>
       <c r="B44" s="32">
         <v>25</v>
       </c>
@@ -2749,7 +2819,7 @@
       <c r="E44" s="37"/>
     </row>
     <row r="45" spans="1:5" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="48"/>
+      <c r="A45" s="50"/>
       <c r="B45" s="32">
         <v>26</v>
       </c>
@@ -2758,7 +2828,7 @@
       <c r="E45" s="37"/>
     </row>
     <row r="46" spans="1:5" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="48"/>
+      <c r="A46" s="50"/>
       <c r="B46" s="32">
         <v>27</v>
       </c>
@@ -2767,7 +2837,7 @@
       <c r="E46" s="37"/>
     </row>
     <row r="47" spans="1:5" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="49"/>
+      <c r="A47" s="51"/>
       <c r="B47" s="32">
         <v>28</v>
       </c>
@@ -2814,7 +2884,7 @@
     </row>
     <row r="3" spans="1:5" ht="42.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:5" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="44" t="s">
+      <c r="A4" s="46" t="s">
         <v>90</v>
       </c>
       <c r="B4" s="28">
@@ -2831,7 +2901,7 @@
       </c>
     </row>
     <row r="5" spans="1:5" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="45"/>
+      <c r="A5" s="47"/>
       <c r="B5" s="32">
         <v>2</v>
       </c>
@@ -2844,7 +2914,7 @@
       </c>
     </row>
     <row r="6" spans="1:5" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="45"/>
+      <c r="A6" s="47"/>
       <c r="B6" s="32">
         <v>3</v>
       </c>
@@ -2859,7 +2929,7 @@
       </c>
     </row>
     <row r="7" spans="1:5" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="45"/>
+      <c r="A7" s="47"/>
       <c r="B7" s="32">
         <v>4</v>
       </c>
@@ -2874,7 +2944,7 @@
       </c>
     </row>
     <row r="8" spans="1:5" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="45"/>
+      <c r="A8" s="47"/>
       <c r="B8" s="32">
         <v>5</v>
       </c>
@@ -2885,7 +2955,7 @@
       </c>
     </row>
     <row r="9" spans="1:5" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="45"/>
+      <c r="A9" s="47"/>
       <c r="B9" s="32">
         <v>6</v>
       </c>
@@ -2896,7 +2966,7 @@
       </c>
     </row>
     <row r="10" spans="1:5" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="45"/>
+      <c r="A10" s="47"/>
       <c r="B10" s="32">
         <v>7</v>
       </c>
@@ -2907,7 +2977,7 @@
       </c>
     </row>
     <row r="11" spans="1:5" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="45"/>
+      <c r="A11" s="47"/>
       <c r="B11" s="32">
         <v>8</v>
       </c>
@@ -2918,7 +2988,7 @@
       </c>
     </row>
     <row r="12" spans="1:5" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="45"/>
+      <c r="A12" s="47"/>
       <c r="B12" s="32">
         <v>9</v>
       </c>
@@ -2929,7 +2999,7 @@
       </c>
     </row>
     <row r="13" spans="1:5" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="45"/>
+      <c r="A13" s="47"/>
       <c r="B13" s="32">
         <v>10</v>
       </c>
@@ -2940,7 +3010,7 @@
       </c>
     </row>
     <row r="14" spans="1:5" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="45"/>
+      <c r="A14" s="47"/>
       <c r="B14" s="32">
         <v>11</v>
       </c>
@@ -2951,7 +3021,7 @@
       </c>
     </row>
     <row r="15" spans="1:5" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="45"/>
+      <c r="A15" s="47"/>
       <c r="B15" s="32">
         <v>12</v>
       </c>
@@ -2962,7 +3032,7 @@
       </c>
     </row>
     <row r="16" spans="1:5" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="45"/>
+      <c r="A16" s="47"/>
       <c r="B16" s="32">
         <v>13</v>
       </c>
@@ -2973,7 +3043,7 @@
       </c>
     </row>
     <row r="17" spans="1:5" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="45"/>
+      <c r="A17" s="47"/>
       <c r="B17" s="32">
         <v>14</v>
       </c>
@@ -2984,7 +3054,7 @@
       </c>
     </row>
     <row r="18" spans="1:5" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="45"/>
+      <c r="A18" s="47"/>
       <c r="B18" s="32">
         <v>15</v>
       </c>
@@ -2993,14 +3063,14 @@
       <c r="E18" s="34"/>
     </row>
     <row r="19" spans="1:5" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="46"/>
+      <c r="A19" s="48"/>
       <c r="B19" s="38"/>
       <c r="C19" s="38"/>
       <c r="D19" s="38"/>
       <c r="E19" s="38"/>
     </row>
     <row r="20" spans="1:5" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="47" t="s">
+      <c r="A20" s="49" t="s">
         <v>91</v>
       </c>
       <c r="B20" s="32">
@@ -3013,7 +3083,7 @@
       </c>
     </row>
     <row r="21" spans="1:5" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="48"/>
+      <c r="A21" s="50"/>
       <c r="B21" s="32">
         <v>2</v>
       </c>
@@ -3024,7 +3094,7 @@
       </c>
     </row>
     <row r="22" spans="1:5" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="48"/>
+      <c r="A22" s="50"/>
       <c r="B22" s="32">
         <v>3</v>
       </c>
@@ -3039,7 +3109,7 @@
       </c>
     </row>
     <row r="23" spans="1:5" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="48"/>
+      <c r="A23" s="50"/>
       <c r="B23" s="32">
         <v>4</v>
       </c>
@@ -3054,7 +3124,7 @@
       </c>
     </row>
     <row r="24" spans="1:5" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="48"/>
+      <c r="A24" s="50"/>
       <c r="B24" s="32">
         <v>5</v>
       </c>
@@ -3069,7 +3139,7 @@
       </c>
     </row>
     <row r="25" spans="1:5" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="48"/>
+      <c r="A25" s="50"/>
       <c r="B25" s="32">
         <v>6</v>
       </c>
@@ -3084,7 +3154,7 @@
       </c>
     </row>
     <row r="26" spans="1:5" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="48"/>
+      <c r="A26" s="50"/>
       <c r="B26" s="32">
         <v>7</v>
       </c>
@@ -3099,7 +3169,7 @@
       </c>
     </row>
     <row r="27" spans="1:5" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="48"/>
+      <c r="A27" s="50"/>
       <c r="B27" s="32">
         <v>8</v>
       </c>
@@ -3114,7 +3184,7 @@
       </c>
     </row>
     <row r="28" spans="1:5" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="48"/>
+      <c r="A28" s="50"/>
       <c r="B28" s="32">
         <v>9</v>
       </c>
@@ -3129,7 +3199,7 @@
       </c>
     </row>
     <row r="29" spans="1:5" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A29" s="48"/>
+      <c r="A29" s="50"/>
       <c r="B29" s="32">
         <v>10</v>
       </c>
@@ -3144,7 +3214,7 @@
       </c>
     </row>
     <row r="30" spans="1:5" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A30" s="48"/>
+      <c r="A30" s="50"/>
       <c r="B30" s="32">
         <v>11</v>
       </c>
@@ -3159,7 +3229,7 @@
       </c>
     </row>
     <row r="31" spans="1:5" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A31" s="48"/>
+      <c r="A31" s="50"/>
       <c r="B31" s="32">
         <v>12</v>
       </c>
@@ -3174,7 +3244,7 @@
       </c>
     </row>
     <row r="32" spans="1:5" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A32" s="48"/>
+      <c r="A32" s="50"/>
       <c r="B32" s="32">
         <v>13</v>
       </c>
@@ -3189,7 +3259,7 @@
       </c>
     </row>
     <row r="33" spans="1:6" ht="42.75" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A33" s="48"/>
+      <c r="A33" s="50"/>
       <c r="B33" s="32">
         <v>14</v>
       </c>
@@ -3204,7 +3274,7 @@
       </c>
     </row>
     <row r="34" spans="1:6" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A34" s="48"/>
+      <c r="A34" s="50"/>
       <c r="B34" s="32">
         <v>15</v>
       </c>
@@ -3219,7 +3289,7 @@
       </c>
     </row>
     <row r="35" spans="1:6" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A35" s="48"/>
+      <c r="A35" s="50"/>
       <c r="B35" s="32">
         <v>16</v>
       </c>
@@ -3237,7 +3307,7 @@
       </c>
     </row>
     <row r="36" spans="1:6" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="48"/>
+      <c r="A36" s="50"/>
       <c r="B36" s="32">
         <v>17</v>
       </c>
@@ -3248,7 +3318,7 @@
       </c>
     </row>
     <row r="37" spans="1:6" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="48"/>
+      <c r="A37" s="50"/>
       <c r="B37" s="32">
         <v>18</v>
       </c>
@@ -3259,7 +3329,7 @@
       </c>
     </row>
     <row r="38" spans="1:6" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="48"/>
+      <c r="A38" s="50"/>
       <c r="B38" s="32">
         <v>19</v>
       </c>
@@ -3268,7 +3338,7 @@
       <c r="E38" s="37"/>
     </row>
     <row r="39" spans="1:6" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="48"/>
+      <c r="A39" s="50"/>
       <c r="B39" s="32">
         <v>20</v>
       </c>
@@ -3277,7 +3347,7 @@
       <c r="E39" s="37"/>
     </row>
     <row r="40" spans="1:6" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="48"/>
+      <c r="A40" s="50"/>
       <c r="B40" s="32">
         <v>21</v>
       </c>
@@ -3286,7 +3356,7 @@
       <c r="E40" s="37"/>
     </row>
     <row r="41" spans="1:6" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="48"/>
+      <c r="A41" s="50"/>
       <c r="B41" s="32">
         <v>22</v>
       </c>
@@ -3295,7 +3365,7 @@
       <c r="E41" s="37"/>
     </row>
     <row r="42" spans="1:6" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="48"/>
+      <c r="A42" s="50"/>
       <c r="B42" s="32">
         <v>23</v>
       </c>
@@ -3304,7 +3374,7 @@
       <c r="E42" s="37"/>
     </row>
     <row r="43" spans="1:6" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="48"/>
+      <c r="A43" s="50"/>
       <c r="B43" s="32">
         <v>24</v>
       </c>
@@ -3313,7 +3383,7 @@
       <c r="E43" s="37"/>
     </row>
     <row r="44" spans="1:6" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="48"/>
+      <c r="A44" s="50"/>
       <c r="B44" s="32">
         <v>25</v>
       </c>
@@ -3322,7 +3392,7 @@
       <c r="E44" s="37"/>
     </row>
     <row r="45" spans="1:6" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="48"/>
+      <c r="A45" s="50"/>
       <c r="B45" s="32">
         <v>26</v>
       </c>
@@ -3331,7 +3401,7 @@
       <c r="E45" s="37"/>
     </row>
     <row r="46" spans="1:6" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="48"/>
+      <c r="A46" s="50"/>
       <c r="B46" s="32">
         <v>27</v>
       </c>
@@ -3340,7 +3410,7 @@
       <c r="E46" s="37"/>
     </row>
     <row r="47" spans="1:6" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="49"/>
+      <c r="A47" s="51"/>
       <c r="B47" s="32">
         <v>28</v>
       </c>
@@ -3359,6 +3429,1411 @@
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28EF462A-10DF-4D5C-9AA9-49B29DE8CF58}">
+  <dimension ref="A1:F47"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="20" customWidth="1"/>
+    <col min="2" max="2" width="8.21875" customWidth="1"/>
+    <col min="3" max="3" width="27.44140625" customWidth="1"/>
+    <col min="4" max="5" width="18.77734375" customWidth="1"/>
+    <col min="6" max="6" width="20.77734375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="54.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B1" s="15" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="63" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="1"/>
+      <c r="C2" s="16" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="42.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="1:5" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="46" t="s">
+        <v>90</v>
+      </c>
+      <c r="B4" s="28">
+        <v>1</v>
+      </c>
+      <c r="C4" s="29"/>
+      <c r="D4" s="30"/>
+      <c r="E4" s="31" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="47"/>
+      <c r="B5" s="32">
+        <v>2</v>
+      </c>
+      <c r="C5" s="33" t="s">
+        <v>87</v>
+      </c>
+      <c r="D5" s="34">
+        <v>1</v>
+      </c>
+      <c r="E5" s="35" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="47"/>
+      <c r="B6" s="32">
+        <v>3</v>
+      </c>
+      <c r="C6" s="33" t="s">
+        <v>39</v>
+      </c>
+      <c r="D6" s="34">
+        <v>1</v>
+      </c>
+      <c r="E6" s="35" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="47"/>
+      <c r="B7" s="32">
+        <v>4</v>
+      </c>
+      <c r="C7" s="33" t="s">
+        <v>27</v>
+      </c>
+      <c r="D7" s="34">
+        <v>0</v>
+      </c>
+      <c r="E7" s="36" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="47"/>
+      <c r="B8" s="32">
+        <v>5</v>
+      </c>
+      <c r="C8" s="33"/>
+      <c r="D8" s="34"/>
+      <c r="E8" s="36" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="47"/>
+      <c r="B9" s="32">
+        <v>6</v>
+      </c>
+      <c r="C9" s="34"/>
+      <c r="D9" s="34"/>
+      <c r="E9" s="35" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="47"/>
+      <c r="B10" s="32">
+        <v>7</v>
+      </c>
+      <c r="C10" s="34"/>
+      <c r="D10" s="34"/>
+      <c r="E10" s="35" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="47"/>
+      <c r="B11" s="32">
+        <v>8</v>
+      </c>
+      <c r="C11" s="34"/>
+      <c r="D11" s="34"/>
+      <c r="E11" s="35" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="47"/>
+      <c r="B12" s="32">
+        <v>9</v>
+      </c>
+      <c r="C12" s="34"/>
+      <c r="D12" s="34"/>
+      <c r="E12" s="35" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="47"/>
+      <c r="B13" s="32">
+        <v>10</v>
+      </c>
+      <c r="C13" s="34"/>
+      <c r="D13" s="34"/>
+      <c r="E13" s="35" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A14" s="47"/>
+      <c r="B14" s="32">
+        <v>11</v>
+      </c>
+      <c r="C14" s="34"/>
+      <c r="D14" s="34"/>
+      <c r="E14" s="35" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="47"/>
+      <c r="B15" s="32">
+        <v>12</v>
+      </c>
+      <c r="C15" s="34"/>
+      <c r="D15" s="34"/>
+      <c r="E15" s="35" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="47"/>
+      <c r="B16" s="32">
+        <v>13</v>
+      </c>
+      <c r="C16" s="34"/>
+      <c r="D16" s="34"/>
+      <c r="E16" s="35" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="47"/>
+      <c r="B17" s="32">
+        <v>14</v>
+      </c>
+      <c r="C17" s="34"/>
+      <c r="D17" s="34"/>
+      <c r="E17" s="35" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="47"/>
+      <c r="B18" s="32">
+        <v>15</v>
+      </c>
+      <c r="C18" s="34"/>
+      <c r="D18" s="34"/>
+      <c r="E18" s="34"/>
+    </row>
+    <row r="19" spans="1:5" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="48"/>
+      <c r="B19" s="38"/>
+      <c r="C19" s="38"/>
+      <c r="D19" s="38"/>
+      <c r="E19" s="38"/>
+    </row>
+    <row r="20" spans="1:5" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="49" t="s">
+        <v>91</v>
+      </c>
+      <c r="B20" s="32">
+        <v>1</v>
+      </c>
+      <c r="C20" s="39"/>
+      <c r="D20" s="41"/>
+      <c r="E20" s="36" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="50"/>
+      <c r="B21" s="32">
+        <v>2</v>
+      </c>
+      <c r="C21" s="37"/>
+      <c r="D21" s="41"/>
+      <c r="E21" s="36" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A22" s="50"/>
+      <c r="B22" s="32">
+        <v>3</v>
+      </c>
+      <c r="C22" s="39" t="s">
+        <v>28</v>
+      </c>
+      <c r="D22" s="41">
+        <v>1</v>
+      </c>
+      <c r="E22" s="36" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A23" s="50"/>
+      <c r="B23" s="32">
+        <v>4</v>
+      </c>
+      <c r="C23" s="39" t="s">
+        <v>38</v>
+      </c>
+      <c r="D23" s="41">
+        <v>1</v>
+      </c>
+      <c r="E23" s="36" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A24" s="50"/>
+      <c r="B24" s="32">
+        <v>5</v>
+      </c>
+      <c r="C24" s="39" t="s">
+        <v>97</v>
+      </c>
+      <c r="D24" s="41">
+        <v>1</v>
+      </c>
+      <c r="E24" s="36" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A25" s="50"/>
+      <c r="B25" s="32">
+        <v>6</v>
+      </c>
+      <c r="C25" s="39" t="s">
+        <v>34</v>
+      </c>
+      <c r="D25" s="41">
+        <v>1</v>
+      </c>
+      <c r="E25" s="36" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A26" s="50"/>
+      <c r="B26" s="32">
+        <v>7</v>
+      </c>
+      <c r="C26" s="39" t="s">
+        <v>30</v>
+      </c>
+      <c r="D26" s="41">
+        <v>0</v>
+      </c>
+      <c r="E26" s="36" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A27" s="50"/>
+      <c r="B27" s="32">
+        <v>8</v>
+      </c>
+      <c r="C27" s="39" t="s">
+        <v>26</v>
+      </c>
+      <c r="D27" s="41">
+        <v>0</v>
+      </c>
+      <c r="E27" s="36" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A28" s="50"/>
+      <c r="B28" s="32">
+        <v>9</v>
+      </c>
+      <c r="C28" s="39" t="s">
+        <v>98</v>
+      </c>
+      <c r="D28" s="41">
+        <v>0</v>
+      </c>
+      <c r="E28" s="36" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A29" s="50"/>
+      <c r="B29" s="32">
+        <v>10</v>
+      </c>
+      <c r="C29" s="39" t="s">
+        <v>102</v>
+      </c>
+      <c r="D29" s="41">
+        <v>1</v>
+      </c>
+      <c r="E29" s="36" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A30" s="50"/>
+      <c r="B30" s="32">
+        <v>11</v>
+      </c>
+      <c r="C30" s="39" t="s">
+        <v>99</v>
+      </c>
+      <c r="D30" s="41">
+        <v>1</v>
+      </c>
+      <c r="E30" s="36" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A31" s="50"/>
+      <c r="B31" s="32">
+        <v>12</v>
+      </c>
+      <c r="C31" s="39" t="s">
+        <v>31</v>
+      </c>
+      <c r="D31" s="41">
+        <v>1</v>
+      </c>
+      <c r="E31" s="36" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A32" s="50"/>
+      <c r="B32" s="32">
+        <v>13</v>
+      </c>
+      <c r="C32" s="39" t="s">
+        <v>100</v>
+      </c>
+      <c r="D32" s="41">
+        <v>1</v>
+      </c>
+      <c r="E32" s="36" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" ht="42.75" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A33" s="50"/>
+      <c r="B33" s="32">
+        <v>14</v>
+      </c>
+      <c r="C33" s="39" t="s">
+        <v>101</v>
+      </c>
+      <c r="D33" s="41">
+        <v>0</v>
+      </c>
+      <c r="E33" s="36" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A34" s="50"/>
+      <c r="B34" s="32">
+        <v>15</v>
+      </c>
+      <c r="C34" s="39" t="s">
+        <v>36</v>
+      </c>
+      <c r="D34" s="41">
+        <v>1</v>
+      </c>
+      <c r="E34" s="36" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A35" s="50"/>
+      <c r="B35" s="32">
+        <v>16</v>
+      </c>
+      <c r="C35" s="39" t="s">
+        <v>104</v>
+      </c>
+      <c r="D35" s="41">
+        <v>1</v>
+      </c>
+      <c r="E35" s="36" t="s">
+        <v>96</v>
+      </c>
+      <c r="F35" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="50"/>
+      <c r="B36" s="32">
+        <v>17</v>
+      </c>
+      <c r="C36" s="37"/>
+      <c r="D36" s="41"/>
+      <c r="E36" s="40" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="50"/>
+      <c r="B37" s="32">
+        <v>18</v>
+      </c>
+      <c r="C37" s="37"/>
+      <c r="D37" s="41"/>
+      <c r="E37" s="40" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="50"/>
+      <c r="B38" s="32">
+        <v>19</v>
+      </c>
+      <c r="C38" s="37"/>
+      <c r="D38" s="41"/>
+      <c r="E38" s="37"/>
+    </row>
+    <row r="39" spans="1:6" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="50"/>
+      <c r="B39" s="32">
+        <v>20</v>
+      </c>
+      <c r="C39" s="37"/>
+      <c r="D39" s="41"/>
+      <c r="E39" s="37"/>
+    </row>
+    <row r="40" spans="1:6" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="50"/>
+      <c r="B40" s="32">
+        <v>21</v>
+      </c>
+      <c r="C40" s="37"/>
+      <c r="D40" s="41"/>
+      <c r="E40" s="37"/>
+    </row>
+    <row r="41" spans="1:6" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="50"/>
+      <c r="B41" s="32">
+        <v>22</v>
+      </c>
+      <c r="C41" s="37"/>
+      <c r="D41" s="41"/>
+      <c r="E41" s="37"/>
+    </row>
+    <row r="42" spans="1:6" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="50"/>
+      <c r="B42" s="32">
+        <v>23</v>
+      </c>
+      <c r="C42" s="37"/>
+      <c r="D42" s="41"/>
+      <c r="E42" s="37"/>
+    </row>
+    <row r="43" spans="1:6" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="50"/>
+      <c r="B43" s="32">
+        <v>24</v>
+      </c>
+      <c r="C43" s="37"/>
+      <c r="D43" s="41"/>
+      <c r="E43" s="37"/>
+    </row>
+    <row r="44" spans="1:6" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="50"/>
+      <c r="B44" s="32">
+        <v>25</v>
+      </c>
+      <c r="C44" s="37"/>
+      <c r="D44" s="37"/>
+      <c r="E44" s="37"/>
+    </row>
+    <row r="45" spans="1:6" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="50"/>
+      <c r="B45" s="32">
+        <v>26</v>
+      </c>
+      <c r="C45" s="37"/>
+      <c r="D45" s="37"/>
+      <c r="E45" s="37"/>
+    </row>
+    <row r="46" spans="1:6" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="50"/>
+      <c r="B46" s="32">
+        <v>27</v>
+      </c>
+      <c r="C46" s="37"/>
+      <c r="D46" s="37"/>
+      <c r="E46" s="37"/>
+    </row>
+    <row r="47" spans="1:6" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="51"/>
+      <c r="B47" s="32">
+        <v>28</v>
+      </c>
+      <c r="C47" s="34"/>
+      <c r="D47" s="34"/>
+      <c r="E47" s="34"/>
+    </row>
+  </sheetData>
+  <dataConsolidate/>
+  <mergeCells count="2">
+    <mergeCell ref="A4:A19"/>
+    <mergeCell ref="A20:A47"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Enter invoicing Company Name in this cell and slogan in cell below" sqref="B1" xr:uid="{812D447D-AD5C-442D-A25C-9DC6447A0083}"/>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{788586AE-C951-4EF7-916C-925BE561D0BE}">
+  <dimension ref="A1:F47"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="20" customWidth="1"/>
+    <col min="2" max="2" width="8.21875" customWidth="1"/>
+    <col min="3" max="3" width="27.44140625" customWidth="1"/>
+    <col min="4" max="5" width="18.77734375" customWidth="1"/>
+    <col min="6" max="6" width="20.77734375" customWidth="1"/>
+    <col min="9" max="9" width="8.88671875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="54.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B1" s="15" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="63" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="1"/>
+      <c r="D2" s="16" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="42.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="1:5" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="46" t="s">
+        <v>90</v>
+      </c>
+      <c r="B4" s="28">
+        <v>1</v>
+      </c>
+      <c r="C4" s="29"/>
+      <c r="D4" s="30"/>
+      <c r="E4" s="31" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="47"/>
+      <c r="B5" s="32">
+        <v>2</v>
+      </c>
+      <c r="C5" s="33"/>
+      <c r="D5" s="42"/>
+      <c r="E5" s="35" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="47"/>
+      <c r="B6" s="32">
+        <v>3</v>
+      </c>
+      <c r="C6" s="33" t="s">
+        <v>39</v>
+      </c>
+      <c r="D6" s="42">
+        <v>0</v>
+      </c>
+      <c r="E6" s="35" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="47"/>
+      <c r="B7" s="32">
+        <v>4</v>
+      </c>
+      <c r="C7" s="33" t="s">
+        <v>87</v>
+      </c>
+      <c r="D7" s="42">
+        <v>1</v>
+      </c>
+      <c r="E7" s="36" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="47"/>
+      <c r="B8" s="32">
+        <v>5</v>
+      </c>
+      <c r="C8" s="33"/>
+      <c r="D8" s="42"/>
+      <c r="E8" s="36" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="47"/>
+      <c r="B9" s="32">
+        <v>6</v>
+      </c>
+      <c r="C9" s="34"/>
+      <c r="D9" s="42"/>
+      <c r="E9" s="35" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="47"/>
+      <c r="B10" s="32">
+        <v>7</v>
+      </c>
+      <c r="C10" s="34"/>
+      <c r="D10" s="42"/>
+      <c r="E10" s="35" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="47"/>
+      <c r="B11" s="32">
+        <v>8</v>
+      </c>
+      <c r="C11" s="34"/>
+      <c r="D11" s="42"/>
+      <c r="E11" s="35" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="47"/>
+      <c r="B12" s="32">
+        <v>9</v>
+      </c>
+      <c r="C12" s="34"/>
+      <c r="D12" s="42"/>
+      <c r="E12" s="35" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="47"/>
+      <c r="B13" s="32">
+        <v>10</v>
+      </c>
+      <c r="C13" s="34"/>
+      <c r="D13" s="42"/>
+      <c r="E13" s="35" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A14" s="47"/>
+      <c r="B14" s="32">
+        <v>11</v>
+      </c>
+      <c r="C14" s="33" t="s">
+        <v>27</v>
+      </c>
+      <c r="D14" s="42">
+        <v>1</v>
+      </c>
+      <c r="E14" s="35" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="47"/>
+      <c r="B15" s="32">
+        <v>12</v>
+      </c>
+      <c r="C15" s="34"/>
+      <c r="D15" s="42"/>
+      <c r="E15" s="35" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="47"/>
+      <c r="B16" s="32">
+        <v>13</v>
+      </c>
+      <c r="C16" s="34"/>
+      <c r="D16" s="42"/>
+      <c r="E16" s="35" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="47"/>
+      <c r="B17" s="32">
+        <v>14</v>
+      </c>
+      <c r="C17" s="34"/>
+      <c r="D17" s="42"/>
+      <c r="E17" s="35" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="47"/>
+      <c r="B18" s="32">
+        <v>15</v>
+      </c>
+      <c r="C18" s="34"/>
+      <c r="D18" s="42"/>
+      <c r="E18" s="40" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="48"/>
+      <c r="B19" s="38"/>
+      <c r="C19" s="38"/>
+      <c r="D19" s="43"/>
+      <c r="E19" s="38"/>
+    </row>
+    <row r="20" spans="1:5" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="49" t="s">
+        <v>91</v>
+      </c>
+      <c r="B20" s="32">
+        <v>1</v>
+      </c>
+      <c r="C20" s="39"/>
+      <c r="D20" s="41"/>
+      <c r="E20" s="36" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="50"/>
+      <c r="B21" s="32">
+        <v>2</v>
+      </c>
+      <c r="C21" s="37"/>
+      <c r="D21" s="41"/>
+      <c r="E21" s="36" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A22" s="50"/>
+      <c r="B22" s="32">
+        <v>3</v>
+      </c>
+      <c r="C22" s="39" t="s">
+        <v>28</v>
+      </c>
+      <c r="D22" s="41">
+        <v>1</v>
+      </c>
+      <c r="E22" s="36" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A23" s="50"/>
+      <c r="B23" s="32">
+        <v>4</v>
+      </c>
+      <c r="C23" s="39" t="s">
+        <v>38</v>
+      </c>
+      <c r="D23" s="41">
+        <v>1</v>
+      </c>
+      <c r="E23" s="36" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A24" s="50"/>
+      <c r="B24" s="32">
+        <v>5</v>
+      </c>
+      <c r="C24" s="39" t="s">
+        <v>97</v>
+      </c>
+      <c r="D24" s="41">
+        <v>1</v>
+      </c>
+      <c r="E24" s="36" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A25" s="50"/>
+      <c r="B25" s="32">
+        <v>6</v>
+      </c>
+      <c r="C25" s="39" t="s">
+        <v>34</v>
+      </c>
+      <c r="D25" s="41">
+        <v>1</v>
+      </c>
+      <c r="E25" s="36" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A26" s="50"/>
+      <c r="B26" s="32">
+        <v>7</v>
+      </c>
+      <c r="C26" s="39" t="s">
+        <v>30</v>
+      </c>
+      <c r="D26" s="41">
+        <v>1</v>
+      </c>
+      <c r="E26" s="36" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A27" s="50"/>
+      <c r="B27" s="32">
+        <v>8</v>
+      </c>
+      <c r="C27" s="39" t="s">
+        <v>26</v>
+      </c>
+      <c r="D27" s="41">
+        <v>0</v>
+      </c>
+      <c r="E27" s="36" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A28" s="50"/>
+      <c r="B28" s="32">
+        <v>9</v>
+      </c>
+      <c r="C28" s="39" t="s">
+        <v>98</v>
+      </c>
+      <c r="D28" s="41">
+        <v>1</v>
+      </c>
+      <c r="E28" s="36" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A29" s="50"/>
+      <c r="B29" s="32">
+        <v>10</v>
+      </c>
+      <c r="C29" s="39" t="s">
+        <v>102</v>
+      </c>
+      <c r="D29" s="41">
+        <v>1</v>
+      </c>
+      <c r="E29" s="36" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A30" s="50"/>
+      <c r="B30" s="32">
+        <v>11</v>
+      </c>
+      <c r="C30" s="39" t="s">
+        <v>99</v>
+      </c>
+      <c r="D30" s="41">
+        <v>1</v>
+      </c>
+      <c r="E30" s="36" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A31" s="50"/>
+      <c r="B31" s="32">
+        <v>12</v>
+      </c>
+      <c r="C31" s="39" t="s">
+        <v>31</v>
+      </c>
+      <c r="D31" s="41"/>
+      <c r="E31" s="36" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A32" s="50"/>
+      <c r="B32" s="32">
+        <v>13</v>
+      </c>
+      <c r="C32" s="39" t="s">
+        <v>100</v>
+      </c>
+      <c r="D32" s="41">
+        <v>1</v>
+      </c>
+      <c r="E32" s="36" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" ht="42.75" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A33" s="50"/>
+      <c r="B33" s="32">
+        <v>14</v>
+      </c>
+      <c r="C33" s="39" t="s">
+        <v>101</v>
+      </c>
+      <c r="D33" s="41">
+        <v>0</v>
+      </c>
+      <c r="E33" s="36" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A34" s="50"/>
+      <c r="B34" s="32">
+        <v>15</v>
+      </c>
+      <c r="C34" s="39" t="s">
+        <v>36</v>
+      </c>
+      <c r="D34" s="41">
+        <v>1</v>
+      </c>
+      <c r="E34" s="36" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A35" s="50"/>
+      <c r="B35" s="32">
+        <v>16</v>
+      </c>
+      <c r="C35" s="39" t="s">
+        <v>104</v>
+      </c>
+      <c r="D35" s="41">
+        <v>0</v>
+      </c>
+      <c r="E35" s="36" t="s">
+        <v>96</v>
+      </c>
+      <c r="F35" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="50"/>
+      <c r="B36" s="32">
+        <v>17</v>
+      </c>
+      <c r="C36" s="39" t="s">
+        <v>105</v>
+      </c>
+      <c r="D36" s="41">
+        <v>1</v>
+      </c>
+      <c r="E36" s="40" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="50"/>
+      <c r="B37" s="32">
+        <v>18</v>
+      </c>
+      <c r="C37" s="39"/>
+      <c r="D37" s="41"/>
+      <c r="E37" s="40"/>
+    </row>
+    <row r="38" spans="1:6" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="50"/>
+      <c r="B38" s="32">
+        <v>19</v>
+      </c>
+      <c r="C38" s="39"/>
+      <c r="D38" s="41"/>
+      <c r="E38" s="37"/>
+    </row>
+    <row r="39" spans="1:6" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="50"/>
+      <c r="B39" s="32">
+        <v>20</v>
+      </c>
+      <c r="C39" s="39"/>
+      <c r="D39" s="41"/>
+      <c r="E39" s="37"/>
+    </row>
+    <row r="40" spans="1:6" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="50"/>
+      <c r="B40" s="32">
+        <v>21</v>
+      </c>
+      <c r="C40" s="39"/>
+      <c r="D40" s="41"/>
+      <c r="E40" s="37"/>
+    </row>
+    <row r="41" spans="1:6" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="50"/>
+      <c r="B41" s="32">
+        <v>22</v>
+      </c>
+      <c r="C41" s="39"/>
+      <c r="D41" s="41"/>
+      <c r="E41" s="37"/>
+    </row>
+    <row r="42" spans="1:6" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="50"/>
+      <c r="B42" s="32">
+        <v>23</v>
+      </c>
+      <c r="C42" s="39"/>
+      <c r="D42" s="41"/>
+      <c r="E42" s="37"/>
+    </row>
+    <row r="43" spans="1:6" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="50"/>
+      <c r="B43" s="32">
+        <v>24</v>
+      </c>
+      <c r="C43" s="39"/>
+      <c r="D43" s="41"/>
+      <c r="E43" s="37"/>
+    </row>
+    <row r="44" spans="1:6" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="50"/>
+      <c r="B44" s="32">
+        <v>25</v>
+      </c>
+      <c r="C44" s="39"/>
+      <c r="D44" s="37"/>
+      <c r="E44" s="37"/>
+    </row>
+    <row r="45" spans="1:6" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="50"/>
+      <c r="B45" s="32">
+        <v>26</v>
+      </c>
+      <c r="C45" s="39"/>
+      <c r="D45" s="37"/>
+      <c r="E45" s="37"/>
+    </row>
+    <row r="46" spans="1:6" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="50"/>
+      <c r="B46" s="32">
+        <v>27</v>
+      </c>
+      <c r="C46" s="39"/>
+      <c r="D46" s="37"/>
+      <c r="E46" s="37"/>
+    </row>
+    <row r="47" spans="1:6" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="51"/>
+      <c r="B47" s="32">
+        <v>28</v>
+      </c>
+      <c r="C47" s="34"/>
+      <c r="D47" s="34"/>
+      <c r="E47" s="34"/>
+    </row>
+  </sheetData>
+  <dataConsolidate/>
+  <mergeCells count="2">
+    <mergeCell ref="A4:A19"/>
+    <mergeCell ref="A20:A47"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Enter invoicing Company Name in this cell and slogan in cell below" sqref="B1" xr:uid="{489AA14F-695C-45CE-B5A4-457E565CF1E7}"/>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50D70402-08A2-4543-BF44-0CBC7600A6DA}">
+  <dimension ref="B1:F21"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="33.77734375" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
+    <col min="5" max="5" width="21.21875" customWidth="1"/>
+    <col min="6" max="6" width="26.6640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:6" ht="33" x14ac:dyDescent="0.45">
+      <c r="B1" s="15" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="2" spans="2:6" ht="33" x14ac:dyDescent="0.3">
+      <c r="B2" s="1"/>
+      <c r="D2" s="16" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="4" spans="2:6" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="B4" s="59" t="s">
+        <v>68</v>
+      </c>
+      <c r="C4" s="59" t="s">
+        <v>108</v>
+      </c>
+      <c r="D4" s="59" t="s">
+        <v>109</v>
+      </c>
+      <c r="E4" s="59" t="s">
+        <v>110</v>
+      </c>
+      <c r="F4" s="60" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="5" spans="2:6" ht="21" x14ac:dyDescent="0.35">
+      <c r="B5" s="52">
+        <v>1</v>
+      </c>
+      <c r="C5" s="57"/>
+      <c r="D5" s="53"/>
+      <c r="E5" s="54" t="s">
+        <v>6</v>
+      </c>
+      <c r="F5" s="56"/>
+    </row>
+    <row r="6" spans="2:6" ht="21" x14ac:dyDescent="0.35">
+      <c r="B6" s="52">
+        <v>2</v>
+      </c>
+      <c r="C6" s="53"/>
+      <c r="D6" s="53"/>
+      <c r="E6" s="54" t="s">
+        <v>92</v>
+      </c>
+      <c r="F6" s="56"/>
+    </row>
+    <row r="7" spans="2:6" ht="21" x14ac:dyDescent="0.35">
+      <c r="B7" s="52">
+        <v>3</v>
+      </c>
+      <c r="C7" s="58" t="s">
+        <v>28</v>
+      </c>
+      <c r="D7" s="53"/>
+      <c r="E7" s="54" t="s">
+        <v>10</v>
+      </c>
+      <c r="F7" s="56"/>
+    </row>
+    <row r="8" spans="2:6" ht="21" x14ac:dyDescent="0.35">
+      <c r="B8" s="52">
+        <v>4</v>
+      </c>
+      <c r="C8" s="58" t="s">
+        <v>38</v>
+      </c>
+      <c r="D8" s="53"/>
+      <c r="E8" s="54" t="s">
+        <v>15</v>
+      </c>
+      <c r="F8" s="56"/>
+    </row>
+    <row r="9" spans="2:6" ht="21" x14ac:dyDescent="0.35">
+      <c r="B9" s="52">
+        <v>5</v>
+      </c>
+      <c r="C9" s="58" t="s">
+        <v>97</v>
+      </c>
+      <c r="D9" s="53"/>
+      <c r="E9" s="54" t="s">
+        <v>14</v>
+      </c>
+      <c r="F9" s="56"/>
+    </row>
+    <row r="10" spans="2:6" ht="21" x14ac:dyDescent="0.35">
+      <c r="B10" s="52">
+        <v>6</v>
+      </c>
+      <c r="C10" s="58" t="s">
+        <v>34</v>
+      </c>
+      <c r="D10" s="53"/>
+      <c r="E10" s="54" t="s">
+        <v>93</v>
+      </c>
+      <c r="F10" s="56"/>
+    </row>
+    <row r="11" spans="2:6" ht="21" x14ac:dyDescent="0.35">
+      <c r="B11" s="52">
+        <v>7</v>
+      </c>
+      <c r="C11" s="58" t="s">
+        <v>30</v>
+      </c>
+      <c r="D11" s="53"/>
+      <c r="E11" s="54" t="s">
+        <v>13</v>
+      </c>
+      <c r="F11" s="56"/>
+    </row>
+    <row r="12" spans="2:6" ht="21" x14ac:dyDescent="0.35">
+      <c r="B12" s="52">
+        <v>8</v>
+      </c>
+      <c r="C12" s="58" t="s">
+        <v>105</v>
+      </c>
+      <c r="D12" s="53"/>
+      <c r="E12" s="54" t="s">
+        <v>2</v>
+      </c>
+      <c r="F12" s="56"/>
+    </row>
+    <row r="13" spans="2:6" ht="21" x14ac:dyDescent="0.35">
+      <c r="B13" s="52">
+        <v>9</v>
+      </c>
+      <c r="C13" s="58" t="s">
+        <v>98</v>
+      </c>
+      <c r="D13" s="53"/>
+      <c r="E13" s="54" t="s">
+        <v>3</v>
+      </c>
+      <c r="F13" s="56"/>
+    </row>
+    <row r="14" spans="2:6" ht="21" x14ac:dyDescent="0.35">
+      <c r="B14" s="52">
+        <v>10</v>
+      </c>
+      <c r="C14" s="58" t="s">
+        <v>102</v>
+      </c>
+      <c r="D14" s="53"/>
+      <c r="E14" s="54" t="s">
+        <v>4</v>
+      </c>
+      <c r="F14" s="56"/>
+    </row>
+    <row r="15" spans="2:6" ht="21" x14ac:dyDescent="0.35">
+      <c r="B15" s="52">
+        <v>11</v>
+      </c>
+      <c r="C15" s="58" t="s">
+        <v>99</v>
+      </c>
+      <c r="D15" s="53"/>
+      <c r="E15" s="54" t="s">
+        <v>94</v>
+      </c>
+      <c r="F15" s="56"/>
+    </row>
+    <row r="16" spans="2:6" ht="21" x14ac:dyDescent="0.35">
+      <c r="B16" s="52">
+        <v>12</v>
+      </c>
+      <c r="C16" s="58"/>
+      <c r="D16" s="53"/>
+      <c r="E16" s="54" t="s">
+        <v>17</v>
+      </c>
+      <c r="F16" s="56"/>
+    </row>
+    <row r="17" spans="2:6" ht="21" x14ac:dyDescent="0.35">
+      <c r="B17" s="52">
+        <v>13</v>
+      </c>
+      <c r="C17" s="58" t="s">
+        <v>100</v>
+      </c>
+      <c r="D17" s="53"/>
+      <c r="E17" s="54" t="s">
+        <v>95</v>
+      </c>
+      <c r="F17" s="56"/>
+    </row>
+    <row r="18" spans="2:6" ht="21" x14ac:dyDescent="0.35">
+      <c r="B18" s="52">
+        <v>14</v>
+      </c>
+      <c r="C18" s="58" t="s">
+        <v>101</v>
+      </c>
+      <c r="D18" s="53"/>
+      <c r="E18" s="54" t="s">
+        <v>22</v>
+      </c>
+      <c r="F18" s="56"/>
+    </row>
+    <row r="19" spans="2:6" ht="21" x14ac:dyDescent="0.35">
+      <c r="B19" s="52">
+        <v>15</v>
+      </c>
+      <c r="C19" s="58" t="s">
+        <v>36</v>
+      </c>
+      <c r="D19" s="53"/>
+      <c r="E19" s="54" t="s">
+        <v>7</v>
+      </c>
+      <c r="F19" s="56"/>
+    </row>
+    <row r="20" spans="2:6" ht="21" x14ac:dyDescent="0.35">
+      <c r="B20" s="52">
+        <v>16</v>
+      </c>
+      <c r="C20" s="58" t="s">
+        <v>104</v>
+      </c>
+      <c r="D20" s="53"/>
+      <c r="E20" s="54" t="s">
+        <v>96</v>
+      </c>
+      <c r="F20" s="56"/>
+    </row>
+    <row r="21" spans="2:6" ht="21" x14ac:dyDescent="0.25">
+      <c r="B21" s="52">
+        <v>17</v>
+      </c>
+      <c r="C21" s="58"/>
+      <c r="D21" s="53"/>
+      <c r="E21" s="55" t="s">
+        <v>112</v>
+      </c>
+      <c r="F21" s="56"/>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Enter invoicing Company Name in this cell and slogan in cell below" sqref="B1" xr:uid="{2CDDD233-BDFA-41DC-ABB0-68DEB62ABCC9}"/>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -6001,7 +7476,7 @@
     </row>
     <row r="3" spans="1:5" ht="42.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:5" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="44" t="s">
+      <c r="A4" s="46" t="s">
         <v>90</v>
       </c>
       <c r="B4" s="28">
@@ -6016,7 +7491,7 @@
       </c>
     </row>
     <row r="5" spans="1:5" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="45"/>
+      <c r="A5" s="47"/>
       <c r="B5" s="32">
         <v>2</v>
       </c>
@@ -6029,7 +7504,7 @@
       </c>
     </row>
     <row r="6" spans="1:5" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="45"/>
+      <c r="A6" s="47"/>
       <c r="B6" s="32">
         <v>3</v>
       </c>
@@ -6042,7 +7517,7 @@
       </c>
     </row>
     <row r="7" spans="1:5" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="45"/>
+      <c r="A7" s="47"/>
       <c r="B7" s="32">
         <v>4</v>
       </c>
@@ -6055,7 +7530,7 @@
       </c>
     </row>
     <row r="8" spans="1:5" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="45"/>
+      <c r="A8" s="47"/>
       <c r="B8" s="32">
         <v>5</v>
       </c>
@@ -6068,7 +7543,7 @@
       </c>
     </row>
     <row r="9" spans="1:5" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="45"/>
+      <c r="A9" s="47"/>
       <c r="B9" s="32">
         <v>6</v>
       </c>
@@ -6079,7 +7554,7 @@
       </c>
     </row>
     <row r="10" spans="1:5" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="45"/>
+      <c r="A10" s="47"/>
       <c r="B10" s="32">
         <v>7</v>
       </c>
@@ -6090,7 +7565,7 @@
       </c>
     </row>
     <row r="11" spans="1:5" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="45"/>
+      <c r="A11" s="47"/>
       <c r="B11" s="32">
         <v>8</v>
       </c>
@@ -6101,7 +7576,7 @@
       </c>
     </row>
     <row r="12" spans="1:5" ht="52.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="45"/>
+      <c r="A12" s="47"/>
       <c r="B12" s="32">
         <v>9</v>
       </c>
@@ -6112,7 +7587,7 @@
       </c>
     </row>
     <row r="13" spans="1:5" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="45"/>
+      <c r="A13" s="47"/>
       <c r="B13" s="32">
         <v>10</v>
       </c>
@@ -6123,7 +7598,7 @@
       </c>
     </row>
     <row r="14" spans="1:5" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="45"/>
+      <c r="A14" s="47"/>
       <c r="B14" s="32">
         <v>11</v>
       </c>
@@ -6134,7 +7609,7 @@
       </c>
     </row>
     <row r="15" spans="1:5" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="45"/>
+      <c r="A15" s="47"/>
       <c r="B15" s="32">
         <v>12</v>
       </c>
@@ -6145,7 +7620,7 @@
       </c>
     </row>
     <row r="16" spans="1:5" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="45"/>
+      <c r="A16" s="47"/>
       <c r="B16" s="32">
         <v>13</v>
       </c>
@@ -6156,7 +7631,7 @@
       </c>
     </row>
     <row r="17" spans="1:5" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="45"/>
+      <c r="A17" s="47"/>
       <c r="B17" s="32">
         <v>14</v>
       </c>
@@ -6167,7 +7642,7 @@
       </c>
     </row>
     <row r="18" spans="1:5" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="45"/>
+      <c r="A18" s="47"/>
       <c r="B18" s="32">
         <v>15</v>
       </c>
@@ -6176,14 +7651,14 @@
       <c r="E18" s="34"/>
     </row>
     <row r="19" spans="1:5" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="46"/>
+      <c r="A19" s="48"/>
       <c r="B19" s="38"/>
       <c r="C19" s="38"/>
       <c r="D19" s="38"/>
       <c r="E19" s="38"/>
     </row>
     <row r="20" spans="1:5" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="47" t="s">
+      <c r="A20" s="49" t="s">
         <v>91</v>
       </c>
       <c r="B20" s="32">
@@ -6196,7 +7671,7 @@
       </c>
     </row>
     <row r="21" spans="1:5" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="48"/>
+      <c r="A21" s="50"/>
       <c r="B21" s="32">
         <v>2</v>
       </c>
@@ -6207,7 +7682,7 @@
       </c>
     </row>
     <row r="22" spans="1:5" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="48"/>
+      <c r="A22" s="50"/>
       <c r="B22" s="32">
         <v>3</v>
       </c>
@@ -6222,7 +7697,7 @@
       </c>
     </row>
     <row r="23" spans="1:5" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="48"/>
+      <c r="A23" s="50"/>
       <c r="B23" s="32">
         <v>4</v>
       </c>
@@ -6237,7 +7712,7 @@
       </c>
     </row>
     <row r="24" spans="1:5" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="48"/>
+      <c r="A24" s="50"/>
       <c r="B24" s="32">
         <v>5</v>
       </c>
@@ -6252,7 +7727,7 @@
       </c>
     </row>
     <row r="25" spans="1:5" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="48"/>
+      <c r="A25" s="50"/>
       <c r="B25" s="32">
         <v>6</v>
       </c>
@@ -6267,7 +7742,7 @@
       </c>
     </row>
     <row r="26" spans="1:5" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="48"/>
+      <c r="A26" s="50"/>
       <c r="B26" s="32">
         <v>7</v>
       </c>
@@ -6282,7 +7757,7 @@
       </c>
     </row>
     <row r="27" spans="1:5" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="48"/>
+      <c r="A27" s="50"/>
       <c r="B27" s="32">
         <v>8</v>
       </c>
@@ -6297,7 +7772,7 @@
       </c>
     </row>
     <row r="28" spans="1:5" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="48"/>
+      <c r="A28" s="50"/>
       <c r="B28" s="32">
         <v>9</v>
       </c>
@@ -6312,7 +7787,7 @@
       </c>
     </row>
     <row r="29" spans="1:5" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A29" s="48"/>
+      <c r="A29" s="50"/>
       <c r="B29" s="32">
         <v>10</v>
       </c>
@@ -6325,7 +7800,7 @@
       </c>
     </row>
     <row r="30" spans="1:5" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A30" s="48"/>
+      <c r="A30" s="50"/>
       <c r="B30" s="32">
         <v>11</v>
       </c>
@@ -6340,7 +7815,7 @@
       </c>
     </row>
     <row r="31" spans="1:5" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A31" s="48"/>
+      <c r="A31" s="50"/>
       <c r="B31" s="32">
         <v>12</v>
       </c>
@@ -6355,7 +7830,7 @@
       </c>
     </row>
     <row r="32" spans="1:5" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A32" s="48"/>
+      <c r="A32" s="50"/>
       <c r="B32" s="32">
         <v>13</v>
       </c>
@@ -6370,7 +7845,7 @@
       </c>
     </row>
     <row r="33" spans="1:5" ht="42.75" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A33" s="48"/>
+      <c r="A33" s="50"/>
       <c r="B33" s="32">
         <v>14</v>
       </c>
@@ -6385,7 +7860,7 @@
       </c>
     </row>
     <row r="34" spans="1:5" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A34" s="48"/>
+      <c r="A34" s="50"/>
       <c r="B34" s="32">
         <v>15</v>
       </c>
@@ -6400,7 +7875,7 @@
       </c>
     </row>
     <row r="35" spans="1:5" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A35" s="48"/>
+      <c r="A35" s="50"/>
       <c r="B35" s="32">
         <v>16</v>
       </c>
@@ -6415,7 +7890,7 @@
       </c>
     </row>
     <row r="36" spans="1:5" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="48"/>
+      <c r="A36" s="50"/>
       <c r="B36" s="32">
         <v>17</v>
       </c>
@@ -6426,7 +7901,7 @@
       </c>
     </row>
     <row r="37" spans="1:5" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="48"/>
+      <c r="A37" s="50"/>
       <c r="B37" s="32">
         <v>18</v>
       </c>
@@ -6437,7 +7912,7 @@
       </c>
     </row>
     <row r="38" spans="1:5" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="48"/>
+      <c r="A38" s="50"/>
       <c r="B38" s="32">
         <v>19</v>
       </c>
@@ -6446,7 +7921,7 @@
       <c r="E38" s="37"/>
     </row>
     <row r="39" spans="1:5" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="48"/>
+      <c r="A39" s="50"/>
       <c r="B39" s="32">
         <v>20</v>
       </c>
@@ -6455,7 +7930,7 @@
       <c r="E39" s="37"/>
     </row>
     <row r="40" spans="1:5" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="48"/>
+      <c r="A40" s="50"/>
       <c r="B40" s="32">
         <v>21</v>
       </c>
@@ -6464,7 +7939,7 @@
       <c r="E40" s="37"/>
     </row>
     <row r="41" spans="1:5" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="48"/>
+      <c r="A41" s="50"/>
       <c r="B41" s="32">
         <v>22</v>
       </c>
@@ -6473,7 +7948,7 @@
       <c r="E41" s="37"/>
     </row>
     <row r="42" spans="1:5" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="48"/>
+      <c r="A42" s="50"/>
       <c r="B42" s="32">
         <v>23</v>
       </c>
@@ -6482,7 +7957,7 @@
       <c r="E42" s="37"/>
     </row>
     <row r="43" spans="1:5" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="48"/>
+      <c r="A43" s="50"/>
       <c r="B43" s="32">
         <v>24</v>
       </c>
@@ -6491,7 +7966,7 @@
       <c r="E43" s="37"/>
     </row>
     <row r="44" spans="1:5" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="48"/>
+      <c r="A44" s="50"/>
       <c r="B44" s="32">
         <v>25</v>
       </c>
@@ -6500,7 +7975,7 @@
       <c r="E44" s="37"/>
     </row>
     <row r="45" spans="1:5" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="48"/>
+      <c r="A45" s="50"/>
       <c r="B45" s="32">
         <v>26</v>
       </c>
@@ -6509,7 +7984,7 @@
       <c r="E45" s="37"/>
     </row>
     <row r="46" spans="1:5" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="48"/>
+      <c r="A46" s="50"/>
       <c r="B46" s="32">
         <v>27</v>
       </c>
@@ -6518,7 +7993,7 @@
       <c r="E46" s="37"/>
     </row>
     <row r="47" spans="1:5" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="49"/>
+      <c r="A47" s="51"/>
       <c r="B47" s="32">
         <v>28</v>
       </c>
@@ -6565,7 +8040,7 @@
     </row>
     <row r="3" spans="1:5" ht="42.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:5" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="44" t="s">
+      <c r="A4" s="46" t="s">
         <v>90</v>
       </c>
       <c r="B4" s="28">
@@ -6580,7 +8055,7 @@
       </c>
     </row>
     <row r="5" spans="1:5" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="45"/>
+      <c r="A5" s="47"/>
       <c r="B5" s="32">
         <v>2</v>
       </c>
@@ -6593,7 +8068,7 @@
       </c>
     </row>
     <row r="6" spans="1:5" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="45"/>
+      <c r="A6" s="47"/>
       <c r="B6" s="32">
         <v>3</v>
       </c>
@@ -6606,7 +8081,7 @@
       </c>
     </row>
     <row r="7" spans="1:5" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="45"/>
+      <c r="A7" s="47"/>
       <c r="B7" s="32">
         <v>4</v>
       </c>
@@ -6619,7 +8094,7 @@
       </c>
     </row>
     <row r="8" spans="1:5" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="45"/>
+      <c r="A8" s="47"/>
       <c r="B8" s="32">
         <v>5</v>
       </c>
@@ -6632,7 +8107,7 @@
       </c>
     </row>
     <row r="9" spans="1:5" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="45"/>
+      <c r="A9" s="47"/>
       <c r="B9" s="32">
         <v>6</v>
       </c>
@@ -6643,7 +8118,7 @@
       </c>
     </row>
     <row r="10" spans="1:5" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="45"/>
+      <c r="A10" s="47"/>
       <c r="B10" s="32">
         <v>7</v>
       </c>
@@ -6654,7 +8129,7 @@
       </c>
     </row>
     <row r="11" spans="1:5" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="45"/>
+      <c r="A11" s="47"/>
       <c r="B11" s="32">
         <v>8</v>
       </c>
@@ -6665,7 +8140,7 @@
       </c>
     </row>
     <row r="12" spans="1:5" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="45"/>
+      <c r="A12" s="47"/>
       <c r="B12" s="32">
         <v>9</v>
       </c>
@@ -6676,7 +8151,7 @@
       </c>
     </row>
     <row r="13" spans="1:5" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="45"/>
+      <c r="A13" s="47"/>
       <c r="B13" s="32">
         <v>10</v>
       </c>
@@ -6687,7 +8162,7 @@
       </c>
     </row>
     <row r="14" spans="1:5" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="45"/>
+      <c r="A14" s="47"/>
       <c r="B14" s="32">
         <v>11</v>
       </c>
@@ -6698,7 +8173,7 @@
       </c>
     </row>
     <row r="15" spans="1:5" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="45"/>
+      <c r="A15" s="47"/>
       <c r="B15" s="32">
         <v>12</v>
       </c>
@@ -6709,7 +8184,7 @@
       </c>
     </row>
     <row r="16" spans="1:5" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="45"/>
+      <c r="A16" s="47"/>
       <c r="B16" s="32">
         <v>13</v>
       </c>
@@ -6720,7 +8195,7 @@
       </c>
     </row>
     <row r="17" spans="1:5" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="45"/>
+      <c r="A17" s="47"/>
       <c r="B17" s="32">
         <v>14</v>
       </c>
@@ -6731,7 +8206,7 @@
       </c>
     </row>
     <row r="18" spans="1:5" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="45"/>
+      <c r="A18" s="47"/>
       <c r="B18" s="32">
         <v>15</v>
       </c>
@@ -6740,14 +8215,14 @@
       <c r="E18" s="34"/>
     </row>
     <row r="19" spans="1:5" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="46"/>
+      <c r="A19" s="48"/>
       <c r="B19" s="38"/>
       <c r="C19" s="38"/>
       <c r="D19" s="38"/>
       <c r="E19" s="38"/>
     </row>
     <row r="20" spans="1:5" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="47" t="s">
+      <c r="A20" s="49" t="s">
         <v>91</v>
       </c>
       <c r="B20" s="32">
@@ -6764,7 +8239,7 @@
       </c>
     </row>
     <row r="21" spans="1:5" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="48"/>
+      <c r="A21" s="50"/>
       <c r="B21" s="32">
         <v>2</v>
       </c>
@@ -6775,7 +8250,7 @@
       </c>
     </row>
     <row r="22" spans="1:5" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="48"/>
+      <c r="A22" s="50"/>
       <c r="B22" s="32">
         <v>3</v>
       </c>
@@ -6790,7 +8265,7 @@
       </c>
     </row>
     <row r="23" spans="1:5" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="48"/>
+      <c r="A23" s="50"/>
       <c r="B23" s="32">
         <v>4</v>
       </c>
@@ -6805,7 +8280,7 @@
       </c>
     </row>
     <row r="24" spans="1:5" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="48"/>
+      <c r="A24" s="50"/>
       <c r="B24" s="32">
         <v>5</v>
       </c>
@@ -6820,7 +8295,7 @@
       </c>
     </row>
     <row r="25" spans="1:5" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="48"/>
+      <c r="A25" s="50"/>
       <c r="B25" s="32">
         <v>6</v>
       </c>
@@ -6835,7 +8310,7 @@
       </c>
     </row>
     <row r="26" spans="1:5" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="48"/>
+      <c r="A26" s="50"/>
       <c r="B26" s="32">
         <v>7</v>
       </c>
@@ -6850,7 +8325,7 @@
       </c>
     </row>
     <row r="27" spans="1:5" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="48"/>
+      <c r="A27" s="50"/>
       <c r="B27" s="32">
         <v>8</v>
       </c>
@@ -6865,7 +8340,7 @@
       </c>
     </row>
     <row r="28" spans="1:5" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="48"/>
+      <c r="A28" s="50"/>
       <c r="B28" s="32">
         <v>9</v>
       </c>
@@ -6880,7 +8355,7 @@
       </c>
     </row>
     <row r="29" spans="1:5" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A29" s="48"/>
+      <c r="A29" s="50"/>
       <c r="B29" s="32">
         <v>10</v>
       </c>
@@ -6895,7 +8370,7 @@
       </c>
     </row>
     <row r="30" spans="1:5" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A30" s="48"/>
+      <c r="A30" s="50"/>
       <c r="B30" s="32">
         <v>11</v>
       </c>
@@ -6910,7 +8385,7 @@
       </c>
     </row>
     <row r="31" spans="1:5" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A31" s="48"/>
+      <c r="A31" s="50"/>
       <c r="B31" s="32">
         <v>12</v>
       </c>
@@ -6925,7 +8400,7 @@
       </c>
     </row>
     <row r="32" spans="1:5" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A32" s="48"/>
+      <c r="A32" s="50"/>
       <c r="B32" s="32">
         <v>13</v>
       </c>
@@ -6940,7 +8415,7 @@
       </c>
     </row>
     <row r="33" spans="1:5" ht="42.75" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A33" s="48"/>
+      <c r="A33" s="50"/>
       <c r="B33" s="32">
         <v>14</v>
       </c>
@@ -6955,7 +8430,7 @@
       </c>
     </row>
     <row r="34" spans="1:5" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A34" s="48"/>
+      <c r="A34" s="50"/>
       <c r="B34" s="32">
         <v>15</v>
       </c>
@@ -6970,7 +8445,7 @@
       </c>
     </row>
     <row r="35" spans="1:5" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A35" s="48"/>
+      <c r="A35" s="50"/>
       <c r="B35" s="32">
         <v>16</v>
       </c>
@@ -6981,7 +8456,7 @@
       </c>
     </row>
     <row r="36" spans="1:5" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="48"/>
+      <c r="A36" s="50"/>
       <c r="B36" s="32">
         <v>17</v>
       </c>
@@ -6992,7 +8467,7 @@
       </c>
     </row>
     <row r="37" spans="1:5" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="48"/>
+      <c r="A37" s="50"/>
       <c r="B37" s="32">
         <v>18</v>
       </c>
@@ -7003,7 +8478,7 @@
       </c>
     </row>
     <row r="38" spans="1:5" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="48"/>
+      <c r="A38" s="50"/>
       <c r="B38" s="32">
         <v>19</v>
       </c>
@@ -7012,7 +8487,7 @@
       <c r="E38" s="37"/>
     </row>
     <row r="39" spans="1:5" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="48"/>
+      <c r="A39" s="50"/>
       <c r="B39" s="32">
         <v>20</v>
       </c>
@@ -7021,7 +8496,7 @@
       <c r="E39" s="37"/>
     </row>
     <row r="40" spans="1:5" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="48"/>
+      <c r="A40" s="50"/>
       <c r="B40" s="32">
         <v>21</v>
       </c>
@@ -7030,7 +8505,7 @@
       <c r="E40" s="37"/>
     </row>
     <row r="41" spans="1:5" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="48"/>
+      <c r="A41" s="50"/>
       <c r="B41" s="32">
         <v>22</v>
       </c>
@@ -7039,7 +8514,7 @@
       <c r="E41" s="37"/>
     </row>
     <row r="42" spans="1:5" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="48"/>
+      <c r="A42" s="50"/>
       <c r="B42" s="32">
         <v>23</v>
       </c>
@@ -7048,7 +8523,7 @@
       <c r="E42" s="37"/>
     </row>
     <row r="43" spans="1:5" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="48"/>
+      <c r="A43" s="50"/>
       <c r="B43" s="32">
         <v>24</v>
       </c>
@@ -7057,7 +8532,7 @@
       <c r="E43" s="37"/>
     </row>
     <row r="44" spans="1:5" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="48"/>
+      <c r="A44" s="50"/>
       <c r="B44" s="32">
         <v>25</v>
       </c>
@@ -7066,7 +8541,7 @@
       <c r="E44" s="37"/>
     </row>
     <row r="45" spans="1:5" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="48"/>
+      <c r="A45" s="50"/>
       <c r="B45" s="32">
         <v>26</v>
       </c>
@@ -7075,7 +8550,7 @@
       <c r="E45" s="37"/>
     </row>
     <row r="46" spans="1:5" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="48"/>
+      <c r="A46" s="50"/>
       <c r="B46" s="32">
         <v>27</v>
       </c>
@@ -7084,7 +8559,7 @@
       <c r="E46" s="37"/>
     </row>
     <row r="47" spans="1:5" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="49"/>
+      <c r="A47" s="51"/>
       <c r="B47" s="32">
         <v>28</v>
       </c>
@@ -7131,7 +8606,7 @@
     </row>
     <row r="3" spans="1:5" ht="42.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:5" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="44" t="s">
+      <c r="A4" s="46" t="s">
         <v>90</v>
       </c>
       <c r="B4" s="28">
@@ -7146,7 +8621,7 @@
       </c>
     </row>
     <row r="5" spans="1:5" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="45"/>
+      <c r="A5" s="47"/>
       <c r="B5" s="32">
         <v>2</v>
       </c>
@@ -7159,7 +8634,7 @@
       </c>
     </row>
     <row r="6" spans="1:5" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="45"/>
+      <c r="A6" s="47"/>
       <c r="B6" s="32">
         <v>3</v>
       </c>
@@ -7172,7 +8647,7 @@
       </c>
     </row>
     <row r="7" spans="1:5" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="45"/>
+      <c r="A7" s="47"/>
       <c r="B7" s="32">
         <v>4</v>
       </c>
@@ -7185,7 +8660,7 @@
       </c>
     </row>
     <row r="8" spans="1:5" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="45"/>
+      <c r="A8" s="47"/>
       <c r="B8" s="32">
         <v>5</v>
       </c>
@@ -7198,7 +8673,7 @@
       </c>
     </row>
     <row r="9" spans="1:5" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="45"/>
+      <c r="A9" s="47"/>
       <c r="B9" s="32">
         <v>6</v>
       </c>
@@ -7209,7 +8684,7 @@
       </c>
     </row>
     <row r="10" spans="1:5" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="45"/>
+      <c r="A10" s="47"/>
       <c r="B10" s="32">
         <v>7</v>
       </c>
@@ -7220,7 +8695,7 @@
       </c>
     </row>
     <row r="11" spans="1:5" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="45"/>
+      <c r="A11" s="47"/>
       <c r="B11" s="32">
         <v>8</v>
       </c>
@@ -7231,7 +8706,7 @@
       </c>
     </row>
     <row r="12" spans="1:5" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="45"/>
+      <c r="A12" s="47"/>
       <c r="B12" s="32">
         <v>9</v>
       </c>
@@ -7242,7 +8717,7 @@
       </c>
     </row>
     <row r="13" spans="1:5" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="45"/>
+      <c r="A13" s="47"/>
       <c r="B13" s="32">
         <v>10</v>
       </c>
@@ -7253,7 +8728,7 @@
       </c>
     </row>
     <row r="14" spans="1:5" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="45"/>
+      <c r="A14" s="47"/>
       <c r="B14" s="32">
         <v>11</v>
       </c>
@@ -7264,7 +8739,7 @@
       </c>
     </row>
     <row r="15" spans="1:5" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="45"/>
+      <c r="A15" s="47"/>
       <c r="B15" s="32">
         <v>12</v>
       </c>
@@ -7275,7 +8750,7 @@
       </c>
     </row>
     <row r="16" spans="1:5" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="45"/>
+      <c r="A16" s="47"/>
       <c r="B16" s="32">
         <v>13</v>
       </c>
@@ -7286,7 +8761,7 @@
       </c>
     </row>
     <row r="17" spans="1:5" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="45"/>
+      <c r="A17" s="47"/>
       <c r="B17" s="32">
         <v>14</v>
       </c>
@@ -7297,7 +8772,7 @@
       </c>
     </row>
     <row r="18" spans="1:5" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="45"/>
+      <c r="A18" s="47"/>
       <c r="B18" s="32">
         <v>15</v>
       </c>
@@ -7306,14 +8781,14 @@
       <c r="E18" s="34"/>
     </row>
     <row r="19" spans="1:5" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="46"/>
+      <c r="A19" s="48"/>
       <c r="B19" s="38"/>
       <c r="C19" s="38"/>
       <c r="D19" s="38"/>
       <c r="E19" s="38"/>
     </row>
     <row r="20" spans="1:5" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="47" t="s">
+      <c r="A20" s="49" t="s">
         <v>91</v>
       </c>
       <c r="B20" s="32">
@@ -7330,7 +8805,7 @@
       </c>
     </row>
     <row r="21" spans="1:5" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="48"/>
+      <c r="A21" s="50"/>
       <c r="B21" s="32">
         <v>2</v>
       </c>
@@ -7341,7 +8816,7 @@
       </c>
     </row>
     <row r="22" spans="1:5" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="48"/>
+      <c r="A22" s="50"/>
       <c r="B22" s="32">
         <v>3</v>
       </c>
@@ -7356,7 +8831,7 @@
       </c>
     </row>
     <row r="23" spans="1:5" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="48"/>
+      <c r="A23" s="50"/>
       <c r="B23" s="32">
         <v>4</v>
       </c>
@@ -7371,7 +8846,7 @@
       </c>
     </row>
     <row r="24" spans="1:5" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="48"/>
+      <c r="A24" s="50"/>
       <c r="B24" s="32">
         <v>5</v>
       </c>
@@ -7386,7 +8861,7 @@
       </c>
     </row>
     <row r="25" spans="1:5" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="48"/>
+      <c r="A25" s="50"/>
       <c r="B25" s="32">
         <v>6</v>
       </c>
@@ -7401,7 +8876,7 @@
       </c>
     </row>
     <row r="26" spans="1:5" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="48"/>
+      <c r="A26" s="50"/>
       <c r="B26" s="32">
         <v>7</v>
       </c>
@@ -7416,7 +8891,7 @@
       </c>
     </row>
     <row r="27" spans="1:5" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="48"/>
+      <c r="A27" s="50"/>
       <c r="B27" s="32">
         <v>8</v>
       </c>
@@ -7431,7 +8906,7 @@
       </c>
     </row>
     <row r="28" spans="1:5" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="48"/>
+      <c r="A28" s="50"/>
       <c r="B28" s="32">
         <v>9</v>
       </c>
@@ -7446,7 +8921,7 @@
       </c>
     </row>
     <row r="29" spans="1:5" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A29" s="48"/>
+      <c r="A29" s="50"/>
       <c r="B29" s="32">
         <v>10</v>
       </c>
@@ -7461,7 +8936,7 @@
       </c>
     </row>
     <row r="30" spans="1:5" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A30" s="48"/>
+      <c r="A30" s="50"/>
       <c r="B30" s="32">
         <v>11</v>
       </c>
@@ -7476,7 +8951,7 @@
       </c>
     </row>
     <row r="31" spans="1:5" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A31" s="48"/>
+      <c r="A31" s="50"/>
       <c r="B31" s="32">
         <v>12</v>
       </c>
@@ -7491,7 +8966,7 @@
       </c>
     </row>
     <row r="32" spans="1:5" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A32" s="48"/>
+      <c r="A32" s="50"/>
       <c r="B32" s="32">
         <v>13</v>
       </c>
@@ -7506,7 +8981,7 @@
       </c>
     </row>
     <row r="33" spans="1:5" ht="42.75" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A33" s="48"/>
+      <c r="A33" s="50"/>
       <c r="B33" s="32">
         <v>14</v>
       </c>
@@ -7521,7 +8996,7 @@
       </c>
     </row>
     <row r="34" spans="1:5" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A34" s="48"/>
+      <c r="A34" s="50"/>
       <c r="B34" s="32">
         <v>15</v>
       </c>
@@ -7536,7 +9011,7 @@
       </c>
     </row>
     <row r="35" spans="1:5" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A35" s="48"/>
+      <c r="A35" s="50"/>
       <c r="B35" s="32">
         <v>16</v>
       </c>
@@ -7547,7 +9022,7 @@
       </c>
     </row>
     <row r="36" spans="1:5" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="48"/>
+      <c r="A36" s="50"/>
       <c r="B36" s="32">
         <v>17</v>
       </c>
@@ -7558,7 +9033,7 @@
       </c>
     </row>
     <row r="37" spans="1:5" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="48"/>
+      <c r="A37" s="50"/>
       <c r="B37" s="32">
         <v>18</v>
       </c>
@@ -7569,7 +9044,7 @@
       </c>
     </row>
     <row r="38" spans="1:5" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="48"/>
+      <c r="A38" s="50"/>
       <c r="B38" s="32">
         <v>19</v>
       </c>
@@ -7578,7 +9053,7 @@
       <c r="E38" s="37"/>
     </row>
     <row r="39" spans="1:5" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="48"/>
+      <c r="A39" s="50"/>
       <c r="B39" s="32">
         <v>20</v>
       </c>
@@ -7587,7 +9062,7 @@
       <c r="E39" s="37"/>
     </row>
     <row r="40" spans="1:5" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="48"/>
+      <c r="A40" s="50"/>
       <c r="B40" s="32">
         <v>21</v>
       </c>
@@ -7596,7 +9071,7 @@
       <c r="E40" s="37"/>
     </row>
     <row r="41" spans="1:5" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="48"/>
+      <c r="A41" s="50"/>
       <c r="B41" s="32">
         <v>22</v>
       </c>
@@ -7605,7 +9080,7 @@
       <c r="E41" s="37"/>
     </row>
     <row r="42" spans="1:5" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="48"/>
+      <c r="A42" s="50"/>
       <c r="B42" s="32">
         <v>23</v>
       </c>
@@ -7614,7 +9089,7 @@
       <c r="E42" s="37"/>
     </row>
     <row r="43" spans="1:5" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="48"/>
+      <c r="A43" s="50"/>
       <c r="B43" s="32">
         <v>24</v>
       </c>
@@ -7623,7 +9098,7 @@
       <c r="E43" s="37"/>
     </row>
     <row r="44" spans="1:5" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="48"/>
+      <c r="A44" s="50"/>
       <c r="B44" s="32">
         <v>25</v>
       </c>
@@ -7632,7 +9107,7 @@
       <c r="E44" s="37"/>
     </row>
     <row r="45" spans="1:5" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="48"/>
+      <c r="A45" s="50"/>
       <c r="B45" s="32">
         <v>26</v>
       </c>
@@ -7641,7 +9116,7 @@
       <c r="E45" s="37"/>
     </row>
     <row r="46" spans="1:5" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="48"/>
+      <c r="A46" s="50"/>
       <c r="B46" s="32">
         <v>27</v>
       </c>
@@ -7650,7 +9125,7 @@
       <c r="E46" s="37"/>
     </row>
     <row r="47" spans="1:5" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="49"/>
+      <c r="A47" s="51"/>
       <c r="B47" s="32">
         <v>28</v>
       </c>
